--- a/research/traditional_assets/database/data/iceland/iceland_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_shipbuilding_marine.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09110726703256139</v>
+        <v>0.09096105249849626</v>
       </c>
       <c r="C2">
-        <v>688.072464670976</v>
+        <v>682.5775410906389</v>
       </c>
       <c r="D2">
-        <v>660.872464670976</v>
+        <v>662.6255410906389</v>
       </c>
       <c r="E2">
-        <v>-269.2</v>
+        <v>-261.952</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.247999999999999</v>
       </c>
       <c r="G2">
         <v>27.2</v>
@@ -1451,28 +1451,28 @@
         <v>11.95</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3645744</v>
       </c>
       <c r="N2">
-        <v>11.95</v>
+        <v>11.5854256</v>
       </c>
       <c r="O2">
-        <v>2.390000000000001</v>
+        <v>2.317085120000001</v>
       </c>
       <c r="P2">
-        <v>9.560000000000002</v>
+        <v>9.268340480000003</v>
       </c>
       <c r="Q2">
-        <v>76.36</v>
+        <v>76.06834048</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09110726703256139</v>
+        <v>0.09147338636211744</v>
       </c>
       <c r="T2">
-        <v>0.859462113536739</v>
+        <v>0.8664072619289551</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>32.7779460104714</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09096105249849626</v>
+        <v>0.09081483796443113</v>
       </c>
       <c r="C3">
-        <v>682.5775410906389</v>
+        <v>677.0919429132196</v>
       </c>
       <c r="D3">
-        <v>662.6255410906389</v>
+        <v>664.3879429132195</v>
       </c>
       <c r="E3">
-        <v>-261.952</v>
+        <v>-254.704</v>
       </c>
       <c r="F3">
-        <v>7.247999999999999</v>
+        <v>14.496</v>
       </c>
       <c r="G3">
         <v>27.2</v>
@@ -1533,28 +1533,28 @@
         <v>11.95</v>
       </c>
       <c r="M3">
-        <v>0.3645744</v>
+        <v>0.7291487999999999</v>
       </c>
       <c r="N3">
-        <v>11.5854256</v>
+        <v>11.2208512</v>
       </c>
       <c r="O3">
-        <v>2.317085120000001</v>
+        <v>2.24417024</v>
       </c>
       <c r="P3">
-        <v>9.268340480000003</v>
+        <v>8.976680960000001</v>
       </c>
       <c r="Q3">
-        <v>76.06834048</v>
+        <v>75.77668095999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09147338636211744</v>
+        <v>0.09184697751472565</v>
       </c>
       <c r="T3">
-        <v>0.8664072619289551</v>
+        <v>0.8734941480434611</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>32.7779460104714</v>
+        <v>16.3889730052357</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09081483796443113</v>
+        <v>0.090704623430366</v>
       </c>
       <c r="C4">
-        <v>677.0919429132196</v>
+        <v>671.1786267583985</v>
       </c>
       <c r="D4">
-        <v>664.3879429132195</v>
+        <v>665.7226267583985</v>
       </c>
       <c r="E4">
-        <v>-254.704</v>
+        <v>-247.456</v>
       </c>
       <c r="F4">
-        <v>14.496</v>
+        <v>21.744</v>
       </c>
       <c r="G4">
         <v>27.2</v>
@@ -1615,45 +1615,45 @@
         <v>11.95</v>
       </c>
       <c r="M4">
-        <v>0.7291487999999999</v>
+        <v>1.1263392</v>
       </c>
       <c r="N4">
-        <v>11.2208512</v>
+        <v>10.8236608</v>
       </c>
       <c r="O4">
-        <v>2.24417024</v>
+        <v>2.164732160000001</v>
       </c>
       <c r="P4">
-        <v>8.976680960000001</v>
+        <v>8.658928640000003</v>
       </c>
       <c r="Q4">
-        <v>75.77668095999999</v>
+        <v>75.45892864</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09184697751472565</v>
+        <v>0.09222827157769692</v>
       </c>
       <c r="T4">
-        <v>0.8734941480434611</v>
+        <v>0.880727155521153</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>16.3889730052357</v>
+        <v>10.60959256323495</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.090704623430366</v>
+        <v>0.09062480889630091</v>
       </c>
       <c r="C5">
-        <v>671.1786267583985</v>
+        <v>664.9005231861457</v>
       </c>
       <c r="D5">
-        <v>665.7226267583985</v>
+        <v>666.6925231861456</v>
       </c>
       <c r="E5">
-        <v>-247.456</v>
+        <v>-240.208</v>
       </c>
       <c r="F5">
-        <v>21.744</v>
+        <v>28.992</v>
       </c>
       <c r="G5">
         <v>27.2</v>
@@ -1697,45 +1697,45 @@
         <v>11.95</v>
       </c>
       <c r="M5">
-        <v>1.1263392</v>
+        <v>1.551072</v>
       </c>
       <c r="N5">
-        <v>10.8236608</v>
+        <v>10.398928</v>
       </c>
       <c r="O5">
-        <v>2.164732160000001</v>
+        <v>2.079785600000001</v>
       </c>
       <c r="P5">
-        <v>8.658928640000003</v>
+        <v>8.319142400000002</v>
       </c>
       <c r="Q5">
-        <v>75.45892864</v>
+        <v>75.1191424</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09222827157769692</v>
+        <v>0.09261750926698011</v>
       </c>
       <c r="T5">
-        <v>0.880727155521153</v>
+        <v>0.8881108506546304</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>10.60959256323495</v>
+        <v>7.704348992180894</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09062480889630091</v>
+        <v>0.09057619436223577</v>
       </c>
       <c r="C6">
-        <v>664.9005231861457</v>
+        <v>658.2446671852892</v>
       </c>
       <c r="D6">
-        <v>666.6925231861456</v>
+        <v>667.2846671852892</v>
       </c>
       <c r="E6">
-        <v>-240.208</v>
+        <v>-232.96</v>
       </c>
       <c r="F6">
-        <v>28.992</v>
+        <v>36.24</v>
       </c>
       <c r="G6">
         <v>27.2</v>
@@ -1779,45 +1779,45 @@
         <v>11.95</v>
       </c>
       <c r="M6">
-        <v>1.551072</v>
+        <v>2.004072</v>
       </c>
       <c r="N6">
-        <v>10.398928</v>
+        <v>9.945928000000002</v>
       </c>
       <c r="O6">
-        <v>2.079785600000001</v>
+        <v>1.989185600000001</v>
       </c>
       <c r="P6">
-        <v>8.319142400000002</v>
+        <v>7.956742400000001</v>
       </c>
       <c r="Q6">
-        <v>75.1191424</v>
+        <v>74.75674239999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09261750926698011</v>
+        <v>0.09301494143393238</v>
       </c>
       <c r="T6">
-        <v>0.8881108506546304</v>
+        <v>0.8956499920014437</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.0428</v>
+        <v>0.04424</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y6">
-        <v>7.704348992180894</v>
+        <v>5.962859617818123</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09057619436223577</v>
+        <v>0.09046997982817066</v>
       </c>
       <c r="C7">
-        <v>658.2446671852892</v>
+        <v>652.2940683781239</v>
       </c>
       <c r="D7">
-        <v>667.2846671852892</v>
+        <v>668.5820683781238</v>
       </c>
       <c r="E7">
-        <v>-232.96</v>
+        <v>-225.712</v>
       </c>
       <c r="F7">
-        <v>36.24</v>
+        <v>43.488</v>
       </c>
       <c r="G7">
         <v>27.2</v>
@@ -1861,28 +1861,28 @@
         <v>11.95</v>
       </c>
       <c r="M7">
-        <v>2.004072</v>
+        <v>2.4048864</v>
       </c>
       <c r="N7">
-        <v>9.945928000000002</v>
+        <v>9.545113600000002</v>
       </c>
       <c r="O7">
-        <v>1.989185600000001</v>
+        <v>1.909022720000001</v>
       </c>
       <c r="P7">
-        <v>7.956742400000001</v>
+        <v>7.636090880000002</v>
       </c>
       <c r="Q7">
-        <v>74.75674239999999</v>
+        <v>74.43609087999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09301494143393238</v>
+        <v>0.09342082960443687</v>
       </c>
       <c r="T7">
-        <v>0.8956499920014437</v>
+        <v>0.9033495406109555</v>
       </c>
       <c r="U7">
         <v>0.0553</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>5.962859617818123</v>
+        <v>4.969049681515102</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09046997982817066</v>
+        <v>0.09050376529410555</v>
       </c>
       <c r="C8">
-        <v>652.2940683781239</v>
+        <v>644.6328350635949</v>
       </c>
       <c r="D8">
-        <v>668.5820683781238</v>
+        <v>668.1688350635949</v>
       </c>
       <c r="E8">
-        <v>-225.712</v>
+        <v>-218.464</v>
       </c>
       <c r="F8">
-        <v>43.48799999999999</v>
+        <v>50.73599999999999</v>
       </c>
       <c r="G8">
         <v>27.2</v>
@@ -1943,45 +1943,45 @@
         <v>11.95</v>
       </c>
       <c r="M8">
-        <v>2.4048864</v>
+        <v>2.9325408</v>
       </c>
       <c r="N8">
-        <v>9.545113600000004</v>
+        <v>9.017459200000003</v>
       </c>
       <c r="O8">
-        <v>1.909022720000001</v>
+        <v>1.803491840000001</v>
       </c>
       <c r="P8">
-        <v>7.636090880000003</v>
+        <v>7.213967360000002</v>
       </c>
       <c r="Q8">
-        <v>74.43609087999999</v>
+        <v>74.01396736</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09342082960443687</v>
+        <v>0.09383544655280165</v>
       </c>
       <c r="T8">
-        <v>0.9033495406109555</v>
+        <v>0.9112146709109943</v>
       </c>
       <c r="U8">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y8">
-        <v>4.969049681515104</v>
+        <v>4.074964617713078</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09050376529410553</v>
+        <v>0.09082075076004043</v>
       </c>
       <c r="C9">
-        <v>644.6328350635951</v>
+        <v>633.5324909580621</v>
       </c>
       <c r="D9">
-        <v>668.168835063595</v>
+        <v>664.3164909580621</v>
       </c>
       <c r="E9">
-        <v>-218.464</v>
+        <v>-211.216</v>
       </c>
       <c r="F9">
-        <v>50.736</v>
+        <v>57.98399999999999</v>
       </c>
       <c r="G9">
         <v>27.2</v>
@@ -2025,45 +2025,45 @@
         <v>11.95</v>
       </c>
       <c r="M9">
-        <v>2.9325408</v>
+        <v>3.7167744</v>
       </c>
       <c r="N9">
-        <v>9.017459200000003</v>
+        <v>8.233225600000003</v>
       </c>
       <c r="O9">
-        <v>1.803491840000001</v>
+        <v>1.646645120000001</v>
       </c>
       <c r="P9">
-        <v>7.213967360000002</v>
+        <v>6.586580480000002</v>
       </c>
       <c r="Q9">
-        <v>74.01396736</v>
+        <v>73.38658047999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09383544655280165</v>
+        <v>0.09425907691308741</v>
       </c>
       <c r="T9">
-        <v>0.9112146709109943</v>
+        <v>0.9192507823045122</v>
       </c>
       <c r="U9">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04624</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.074964617713077</v>
+        <v>3.21515344057471</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09082075076004043</v>
+        <v>0.09134653622597527</v>
       </c>
       <c r="C10">
-        <v>633.5324909580621</v>
+        <v>619.9916093561206</v>
       </c>
       <c r="D10">
-        <v>664.3164909580621</v>
+        <v>658.0236093561206</v>
       </c>
       <c r="E10">
-        <v>-211.216</v>
+        <v>-203.968</v>
       </c>
       <c r="F10">
-        <v>57.98399999999999</v>
+        <v>65.232</v>
       </c>
       <c r="G10">
         <v>27.2</v>
@@ -2107,45 +2107,45 @@
         <v>11.95</v>
       </c>
       <c r="M10">
-        <v>3.7167744</v>
+        <v>4.6901808</v>
       </c>
       <c r="N10">
-        <v>8.233225600000003</v>
+        <v>7.259819200000003</v>
       </c>
       <c r="O10">
-        <v>1.646645120000001</v>
+        <v>1.451963840000001</v>
       </c>
       <c r="P10">
-        <v>6.586580480000002</v>
+        <v>5.807855360000002</v>
       </c>
       <c r="Q10">
-        <v>73.38658047999999</v>
+        <v>72.60785536</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09425907691308741</v>
+        <v>0.09469201783074206</v>
       </c>
       <c r="T10">
-        <v>0.9192507823045122</v>
+        <v>0.9274635115308545</v>
       </c>
       <c r="U10">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.21515344057471</v>
+        <v>2.547876192747197</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09134653622597527</v>
+        <v>0.09168512169191016</v>
       </c>
       <c r="C11">
-        <v>619.9916093561206</v>
+        <v>608.7539615218648</v>
       </c>
       <c r="D11">
-        <v>658.0236093561206</v>
+        <v>654.0339615218647</v>
       </c>
       <c r="E11">
-        <v>-203.968</v>
+        <v>-196.72</v>
       </c>
       <c r="F11">
-        <v>65.232</v>
+        <v>72.47999999999999</v>
       </c>
       <c r="G11">
         <v>27.2</v>
@@ -2189,45 +2189,45 @@
         <v>11.95</v>
       </c>
       <c r="M11">
-        <v>4.6901808</v>
+        <v>5.493983999999999</v>
       </c>
       <c r="N11">
-        <v>7.259819200000003</v>
+        <v>6.456016000000004</v>
       </c>
       <c r="O11">
-        <v>1.451963840000001</v>
+        <v>1.291203200000001</v>
       </c>
       <c r="P11">
-        <v>5.807855360000002</v>
+        <v>5.164812800000003</v>
       </c>
       <c r="Q11">
-        <v>72.60785536</v>
+        <v>71.9648128</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09469201783074206</v>
+        <v>0.09513457965767795</v>
       </c>
       <c r="T11">
-        <v>0.9274635115308545</v>
+        <v>0.9358587458511157</v>
       </c>
       <c r="U11">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.547876192747197</v>
+        <v>2.175106443702786</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09168512169191018</v>
+        <v>0.09299250715784503</v>
       </c>
       <c r="C12">
-        <v>608.7539615218645</v>
+        <v>586.5443472767186</v>
       </c>
       <c r="D12">
-        <v>654.0339615218645</v>
+        <v>639.0723472767185</v>
       </c>
       <c r="E12">
-        <v>-196.72</v>
+        <v>-189.472</v>
       </c>
       <c r="F12">
-        <v>72.48</v>
+        <v>79.72799999999999</v>
       </c>
       <c r="G12">
         <v>27.2</v>
@@ -2271,45 +2271,45 @@
         <v>11.95</v>
       </c>
       <c r="M12">
-        <v>5.493984000000001</v>
+        <v>7.17552</v>
       </c>
       <c r="N12">
-        <v>6.456016000000002</v>
+        <v>4.774480000000003</v>
       </c>
       <c r="O12">
-        <v>1.2912032</v>
+        <v>0.9548960000000006</v>
       </c>
       <c r="P12">
-        <v>5.164812800000002</v>
+        <v>3.819584000000003</v>
       </c>
       <c r="Q12">
-        <v>71.9648128</v>
+        <v>70.619584</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09513457965767796</v>
+        <v>0.0955870866942079</v>
       </c>
       <c r="T12">
-        <v>0.9358587458511158</v>
+        <v>0.944442637122394</v>
       </c>
       <c r="U12">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>2.175106443702785</v>
+        <v>1.665384529622941</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09299250715784503</v>
+        <v>0.09316389262377991</v>
       </c>
       <c r="C13">
-        <v>586.5443472767186</v>
+        <v>577.3856226574267</v>
       </c>
       <c r="D13">
-        <v>639.0723472767185</v>
+        <v>637.1616226574266</v>
       </c>
       <c r="E13">
-        <v>-189.472</v>
+        <v>-182.224</v>
       </c>
       <c r="F13">
-        <v>79.72799999999999</v>
+        <v>86.97599999999998</v>
       </c>
       <c r="G13">
         <v>27.2</v>
@@ -2353,28 +2353,28 @@
         <v>11.95</v>
       </c>
       <c r="M13">
-        <v>7.17552</v>
+        <v>7.827839999999998</v>
       </c>
       <c r="N13">
-        <v>4.774480000000003</v>
+        <v>4.122160000000004</v>
       </c>
       <c r="O13">
-        <v>0.9548960000000006</v>
+        <v>0.8244320000000009</v>
       </c>
       <c r="P13">
-        <v>3.819584000000003</v>
+        <v>3.297728000000004</v>
       </c>
       <c r="Q13">
-        <v>70.619584</v>
+        <v>70.097728</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0955870866942079</v>
+        <v>0.09604987798156808</v>
       </c>
       <c r="T13">
-        <v>0.944442637122394</v>
+        <v>0.953221616831656</v>
       </c>
       <c r="U13">
         <v>0.09</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>1.665384529622941</v>
+        <v>1.526602485487696</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09316389262377991</v>
+        <v>0.09992210155791929</v>
       </c>
       <c r="C14">
-        <v>577.3856226574267</v>
+        <v>502.9401086455234</v>
       </c>
       <c r="D14">
-        <v>637.1616226574266</v>
+        <v>569.9641086455233</v>
       </c>
       <c r="E14">
-        <v>-182.224</v>
+        <v>-174.976</v>
       </c>
       <c r="F14">
-        <v>86.97599999999998</v>
+        <v>94.224</v>
       </c>
       <c r="G14">
         <v>27.2</v>
@@ -2435,45 +2435,45 @@
         <v>11.95</v>
       </c>
       <c r="M14">
-        <v>7.827839999999998</v>
+        <v>13.8320832</v>
       </c>
       <c r="N14">
-        <v>4.122160000000004</v>
+        <v>-1.882083199999999</v>
       </c>
       <c r="O14">
-        <v>0.8244320000000009</v>
+        <v>-0.3764166399999997</v>
       </c>
       <c r="P14">
-        <v>3.297728000000004</v>
+        <v>-1.505666559999999</v>
       </c>
       <c r="Q14">
-        <v>70.097728</v>
+        <v>65.29433344</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09604987798156808</v>
+        <v>0.09670754359376174</v>
       </c>
       <c r="T14">
-        <v>0.953221616831656</v>
+        <v>0.965697290472491</v>
       </c>
       <c r="U14">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V14">
-        <v>0.2</v>
+        <v>0.1727866992587205</v>
       </c>
       <c r="W14">
-        <v>0.07199999999999999</v>
+        <v>0.1214349125488198</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y14">
-        <v>1.526602485487696</v>
+        <v>0.8639334962936025</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09992210155791929</v>
+        <v>0.1009321015579193</v>
       </c>
       <c r="C15">
-        <v>502.9401086455234</v>
+        <v>486.8480995178446</v>
       </c>
       <c r="D15">
-        <v>569.9641086455233</v>
+        <v>561.1200995178446</v>
       </c>
       <c r="E15">
-        <v>-174.976</v>
+        <v>-167.728</v>
       </c>
       <c r="F15">
-        <v>94.224</v>
+        <v>101.472</v>
       </c>
       <c r="G15">
         <v>27.2</v>
@@ -2517,37 +2517,37 @@
         <v>11.95</v>
       </c>
       <c r="M15">
-        <v>13.8320832</v>
+        <v>14.8960896</v>
       </c>
       <c r="N15">
-        <v>-1.882083199999999</v>
+        <v>-2.946089600000001</v>
       </c>
       <c r="O15">
-        <v>-0.3764166399999997</v>
+        <v>-0.5892179200000002</v>
       </c>
       <c r="P15">
-        <v>-1.505666559999999</v>
+        <v>-2.35687168</v>
       </c>
       <c r="Q15">
-        <v>65.29433344</v>
+        <v>64.44312832</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09670754359376174</v>
+        <v>0.09729949177508457</v>
       </c>
       <c r="T15">
-        <v>0.965697290472491</v>
+        <v>0.9769263287337991</v>
       </c>
       <c r="U15">
         <v>0.1468</v>
       </c>
       <c r="V15">
-        <v>0.1727866992587205</v>
+        <v>0.1604447921688119</v>
       </c>
       <c r="W15">
-        <v>0.1214349125488198</v>
+        <v>0.1232467045096184</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.8639334962936025</v>
+        <v>0.8022239608440593</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1009321015579193</v>
+        <v>0.1103157869250676</v>
       </c>
       <c r="C16">
-        <v>486.8480995178446</v>
+        <v>408.8997317533389</v>
       </c>
       <c r="D16">
-        <v>561.1200995178446</v>
+        <v>490.4197317533389</v>
       </c>
       <c r="E16">
-        <v>-167.728</v>
+        <v>-160.48</v>
       </c>
       <c r="F16">
-        <v>101.472</v>
+        <v>108.72</v>
       </c>
       <c r="G16">
         <v>27.2</v>
@@ -2599,45 +2599,45 @@
         <v>11.95</v>
       </c>
       <c r="M16">
-        <v>14.8960896</v>
+        <v>21.830976</v>
       </c>
       <c r="N16">
-        <v>-2.946089600000001</v>
+        <v>-9.880976</v>
       </c>
       <c r="O16">
-        <v>-0.5892179200000002</v>
+        <v>-1.9761952</v>
       </c>
       <c r="P16">
-        <v>-2.35687168</v>
+        <v>-7.9047808</v>
       </c>
       <c r="Q16">
-        <v>64.44312832</v>
+        <v>58.8952192</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09729949177508457</v>
+        <v>0.0982273509337895</v>
       </c>
       <c r="T16">
-        <v>0.9769263287337991</v>
+        <v>0.9945274741092605</v>
       </c>
       <c r="U16">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.1604447921688119</v>
+        <v>0.1094774690787989</v>
       </c>
       <c r="W16">
-        <v>0.1232467045096184</v>
+        <v>0.1788169242089772</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y16">
-        <v>0.8022239608440593</v>
+        <v>0.5473873453939944</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1103157869250676</v>
+        <v>0.1118657869250677</v>
       </c>
       <c r="C17">
-        <v>408.8997317533389</v>
+        <v>391.6529735319372</v>
       </c>
       <c r="D17">
-        <v>490.4197317533389</v>
+        <v>480.4209735319371</v>
       </c>
       <c r="E17">
-        <v>-160.48</v>
+        <v>-153.232</v>
       </c>
       <c r="F17">
-        <v>108.72</v>
+        <v>115.968</v>
       </c>
       <c r="G17">
         <v>27.2</v>
@@ -2681,37 +2681,37 @@
         <v>11.95</v>
       </c>
       <c r="M17">
-        <v>21.830976</v>
+        <v>23.2863744</v>
       </c>
       <c r="N17">
-        <v>-9.880975999999993</v>
+        <v>-11.3363744</v>
       </c>
       <c r="O17">
-        <v>-1.976195199999999</v>
+        <v>-2.26727488</v>
       </c>
       <c r="P17">
-        <v>-7.904780799999995</v>
+        <v>-9.069099519999998</v>
       </c>
       <c r="Q17">
-        <v>58.8952192</v>
+        <v>57.73090048</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0982273509337895</v>
+        <v>0.09885148606395366</v>
       </c>
       <c r="T17">
-        <v>0.9945274741092605</v>
+        <v>1.006367086896276</v>
       </c>
       <c r="U17">
         <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.1094774690787989</v>
+        <v>0.102635127261374</v>
       </c>
       <c r="W17">
-        <v>0.1788169242089772</v>
+        <v>0.1801908664459161</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.5473873453939946</v>
+        <v>0.5131756363068698</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1118657869250677</v>
+        <v>0.1194762222764646</v>
       </c>
       <c r="C18">
-        <v>391.6529735319372</v>
+        <v>340.6886390876037</v>
       </c>
       <c r="D18">
-        <v>480.4209735319371</v>
+        <v>436.7046390876038</v>
       </c>
       <c r="E18">
-        <v>-153.232</v>
+        <v>-145.984</v>
       </c>
       <c r="F18">
-        <v>115.968</v>
+        <v>123.216</v>
       </c>
       <c r="G18">
         <v>27.2</v>
@@ -2763,45 +2763,45 @@
         <v>11.95</v>
       </c>
       <c r="M18">
-        <v>23.2863744</v>
+        <v>29.0543328</v>
       </c>
       <c r="N18">
-        <v>-11.3363744</v>
+        <v>-17.1043328</v>
       </c>
       <c r="O18">
-        <v>-2.26727488</v>
+        <v>-3.42086656</v>
       </c>
       <c r="P18">
-        <v>-9.069099519999998</v>
+        <v>-13.68346624</v>
       </c>
       <c r="Q18">
-        <v>57.73090048</v>
+        <v>53.11653376</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09885148606395366</v>
+        <v>0.09962371523508201</v>
       </c>
       <c r="T18">
-        <v>1.006367086896276</v>
+        <v>1.021015988916247</v>
       </c>
       <c r="U18">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.102635127261374</v>
+        <v>0.08225967591312233</v>
       </c>
       <c r="W18">
-        <v>0.1801908664459161</v>
+        <v>0.2164031684196858</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y18">
-        <v>0.5131756363068698</v>
+        <v>0.4112983795656117</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1194762222764646</v>
+        <v>0.1213762222764646</v>
       </c>
       <c r="C19">
-        <v>340.6886390876037</v>
+        <v>323.7400551011982</v>
       </c>
       <c r="D19">
-        <v>436.7046390876038</v>
+        <v>427.0040551011982</v>
       </c>
       <c r="E19">
-        <v>-145.984</v>
+        <v>-138.736</v>
       </c>
       <c r="F19">
-        <v>123.216</v>
+        <v>130.464</v>
       </c>
       <c r="G19">
         <v>27.2</v>
@@ -2845,37 +2845,37 @@
         <v>11.95</v>
       </c>
       <c r="M19">
-        <v>29.0543328</v>
+        <v>30.7634112</v>
       </c>
       <c r="N19">
-        <v>-17.1043328</v>
+        <v>-18.8134112</v>
       </c>
       <c r="O19">
-        <v>-3.42086656</v>
+        <v>-3.76268224</v>
       </c>
       <c r="P19">
-        <v>-13.68346624</v>
+        <v>-15.05072896</v>
       </c>
       <c r="Q19">
-        <v>53.11653376</v>
+        <v>51.74927104</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09962371523508201</v>
+        <v>0.1002801020062415</v>
       </c>
       <c r="T19">
-        <v>1.021015988916247</v>
+        <v>1.033467403415226</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.08225967591312233</v>
+        <v>0.07768969391794889</v>
       </c>
       <c r="W19">
-        <v>0.2164031684196858</v>
+        <v>0.2174807701741477</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.4112983795656117</v>
+        <v>0.3884484695897444</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1213762222764646</v>
+        <v>0.1232762222764646</v>
       </c>
       <c r="C20">
-        <v>323.7400551011984</v>
+        <v>307.2130671213507</v>
       </c>
       <c r="D20">
-        <v>427.0040551011984</v>
+        <v>417.7250671213507</v>
       </c>
       <c r="E20">
-        <v>-138.736</v>
+        <v>-131.488</v>
       </c>
       <c r="F20">
-        <v>130.464</v>
+        <v>137.712</v>
       </c>
       <c r="G20">
         <v>27.2</v>
@@ -2927,37 +2927,37 @@
         <v>11.95</v>
       </c>
       <c r="M20">
-        <v>30.7634112</v>
+        <v>32.4724896</v>
       </c>
       <c r="N20">
-        <v>-18.8134112</v>
+        <v>-20.52248959999999</v>
       </c>
       <c r="O20">
-        <v>-3.76268224</v>
+        <v>-4.104497919999999</v>
       </c>
       <c r="P20">
-        <v>-15.05072896</v>
+        <v>-16.41799167999999</v>
       </c>
       <c r="Q20">
-        <v>51.74927104</v>
+        <v>50.38200832</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1002801020062415</v>
+        <v>0.1009526958581704</v>
       </c>
       <c r="T20">
-        <v>1.033467403415226</v>
+        <v>1.046226260247513</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.07768969391794889</v>
+        <v>0.07360076265910948</v>
       </c>
       <c r="W20">
-        <v>0.2174807701741477</v>
+        <v>0.218444940164982</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3884484695897444</v>
+        <v>0.3680038132955474</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1232762222764646</v>
+        <v>0.1251762222764647</v>
       </c>
       <c r="C21">
-        <v>307.2130671213507</v>
+        <v>291.080775287941</v>
       </c>
       <c r="D21">
-        <v>417.7250671213507</v>
+        <v>408.840775287941</v>
       </c>
       <c r="E21">
-        <v>-131.488</v>
+        <v>-124.24</v>
       </c>
       <c r="F21">
-        <v>137.712</v>
+        <v>144.96</v>
       </c>
       <c r="G21">
         <v>27.2</v>
@@ -3009,37 +3009,37 @@
         <v>11.95</v>
       </c>
       <c r="M21">
-        <v>32.4724896</v>
+        <v>34.18156800000001</v>
       </c>
       <c r="N21">
-        <v>-20.52248959999999</v>
+        <v>-22.231568</v>
       </c>
       <c r="O21">
-        <v>-4.104497919999999</v>
+        <v>-4.446313600000001</v>
       </c>
       <c r="P21">
-        <v>-16.41799167999999</v>
+        <v>-17.7852544</v>
       </c>
       <c r="Q21">
-        <v>50.38200832</v>
+        <v>49.0147456</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1009526958581704</v>
+        <v>0.1016421045563976</v>
       </c>
       <c r="T21">
-        <v>1.046226260247513</v>
+        <v>1.059304088500606</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.07360076265910948</v>
+        <v>0.06992072452615399</v>
       </c>
       <c r="W21">
-        <v>0.218444940164982</v>
+        <v>0.2193126931567329</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3680038132955474</v>
+        <v>0.3496036226307699</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1251762222764647</v>
+        <v>0.1270762222764646</v>
       </c>
       <c r="C22">
-        <v>291.080775287941</v>
+        <v>275.318520537518</v>
       </c>
       <c r="D22">
-        <v>408.840775287941</v>
+        <v>400.326520537518</v>
       </c>
       <c r="E22">
-        <v>-124.24</v>
+        <v>-116.992</v>
       </c>
       <c r="F22">
-        <v>144.96</v>
+        <v>152.208</v>
       </c>
       <c r="G22">
         <v>27.2</v>
@@ -3091,37 +3091,37 @@
         <v>11.95</v>
       </c>
       <c r="M22">
-        <v>34.18156800000001</v>
+        <v>35.8906464</v>
       </c>
       <c r="N22">
-        <v>-22.231568</v>
+        <v>-23.9406464</v>
       </c>
       <c r="O22">
-        <v>-4.446313600000001</v>
+        <v>-4.78812928</v>
       </c>
       <c r="P22">
-        <v>-17.7852544</v>
+        <v>-19.15251712</v>
       </c>
       <c r="Q22">
-        <v>49.0147456</v>
+        <v>47.64748288</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1016421045563976</v>
+        <v>0.1023489666393899</v>
       </c>
       <c r="T22">
-        <v>1.059304088500606</v>
+        <v>1.072713001013272</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.06992072452615399</v>
+        <v>0.06659116621538476</v>
       </c>
       <c r="W22">
-        <v>0.2193126931567329</v>
+        <v>0.2200978030064123</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3496036226307699</v>
+        <v>0.3329558310769237</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1270762222764646</v>
+        <v>0.1289762222764647</v>
       </c>
       <c r="C23">
-        <v>275.318520537518</v>
+        <v>259.9036560363435</v>
       </c>
       <c r="D23">
-        <v>400.326520537518</v>
+        <v>392.1596560363435</v>
       </c>
       <c r="E23">
-        <v>-116.992</v>
+        <v>-109.744</v>
       </c>
       <c r="F23">
-        <v>152.208</v>
+        <v>159.456</v>
       </c>
       <c r="G23">
         <v>27.2</v>
@@ -3173,37 +3173,37 @@
         <v>11.95</v>
       </c>
       <c r="M23">
-        <v>35.8906464</v>
+        <v>37.5997248</v>
       </c>
       <c r="N23">
-        <v>-23.9406464</v>
+        <v>-25.64972479999999</v>
       </c>
       <c r="O23">
-        <v>-4.78812928</v>
+        <v>-5.12994496</v>
       </c>
       <c r="P23">
-        <v>-19.15251712</v>
+        <v>-20.51977983999999</v>
       </c>
       <c r="Q23">
-        <v>47.64748288</v>
+        <v>46.28022016</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1023489666393899</v>
+        <v>0.103073953391177</v>
       </c>
       <c r="T23">
-        <v>1.072713001013272</v>
+        <v>1.086465731795494</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.06659116621538476</v>
+        <v>0.06356429502377636</v>
       </c>
       <c r="W23">
-        <v>0.2200978030064123</v>
+        <v>0.2208115392333936</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3329558310769237</v>
+        <v>0.3178214751188818</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1289762222764647</v>
+        <v>0.1308762222764646</v>
       </c>
       <c r="C24">
-        <v>259.9036560363435</v>
+        <v>244.8153460313906</v>
       </c>
       <c r="D24">
-        <v>392.1596560363435</v>
+        <v>384.3193460313906</v>
       </c>
       <c r="E24">
-        <v>-109.744</v>
+        <v>-102.496</v>
       </c>
       <c r="F24">
-        <v>159.456</v>
+        <v>166.704</v>
       </c>
       <c r="G24">
         <v>27.2</v>
@@ -3255,37 +3255,37 @@
         <v>11.95</v>
       </c>
       <c r="M24">
-        <v>37.5997248</v>
+        <v>39.30880320000001</v>
       </c>
       <c r="N24">
-        <v>-25.64972479999999</v>
+        <v>-27.3588032</v>
       </c>
       <c r="O24">
-        <v>-5.12994496</v>
+        <v>-5.471760640000001</v>
       </c>
       <c r="P24">
-        <v>-20.51977983999999</v>
+        <v>-21.88704256</v>
       </c>
       <c r="Q24">
-        <v>46.28022016</v>
+        <v>44.91295743999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.103073953391177</v>
+        <v>0.1038177709676858</v>
       </c>
       <c r="T24">
-        <v>1.086465731795494</v>
+        <v>1.100575676364267</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.06356429502377636</v>
+        <v>0.0608006300227426</v>
       </c>
       <c r="W24">
-        <v>0.2208115392333936</v>
+        <v>0.2214632114406373</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3178214751188818</v>
+        <v>0.3040031501137129</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1308762222764646</v>
+        <v>0.1327762222764647</v>
       </c>
       <c r="C25">
-        <v>244.8153460313906</v>
+        <v>230.0343883573995</v>
       </c>
       <c r="D25">
-        <v>384.3193460313906</v>
+        <v>376.7863883573995</v>
       </c>
       <c r="E25">
-        <v>-102.496</v>
+        <v>-95.24799999999999</v>
       </c>
       <c r="F25">
-        <v>166.704</v>
+        <v>173.952</v>
       </c>
       <c r="G25">
         <v>27.2</v>
@@ -3337,37 +3337,37 @@
         <v>11.95</v>
       </c>
       <c r="M25">
-        <v>39.30880320000001</v>
+        <v>41.0178816</v>
       </c>
       <c r="N25">
-        <v>-27.3588032</v>
+        <v>-29.0678816</v>
       </c>
       <c r="O25">
-        <v>-5.471760640000001</v>
+        <v>-5.81357632</v>
       </c>
       <c r="P25">
-        <v>-21.88704256</v>
+        <v>-23.25430528</v>
       </c>
       <c r="Q25">
-        <v>44.91295743999999</v>
+        <v>43.54569472</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1038177709676858</v>
+        <v>0.1045811626909448</v>
       </c>
       <c r="T25">
-        <v>1.100575676364267</v>
+        <v>1.115056935263796</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.0608006300227426</v>
+        <v>0.05826727043846167</v>
       </c>
       <c r="W25">
-        <v>0.2214632114406373</v>
+        <v>0.2220605776306107</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3040031501137129</v>
+        <v>0.2913363521923082</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1327762222764646</v>
+        <v>0.1346762222764646</v>
       </c>
       <c r="C26">
-        <v>230.0343883573997</v>
+        <v>215.5430574166525</v>
       </c>
       <c r="D26">
-        <v>376.7863883573997</v>
+        <v>369.5430574166525</v>
       </c>
       <c r="E26">
-        <v>-95.24800000000002</v>
+        <v>-88</v>
       </c>
       <c r="F26">
-        <v>173.952</v>
+        <v>181.2</v>
       </c>
       <c r="G26">
         <v>27.2</v>
@@ -3419,37 +3419,37 @@
         <v>11.95</v>
       </c>
       <c r="M26">
-        <v>41.0178816</v>
+        <v>42.72696</v>
       </c>
       <c r="N26">
-        <v>-29.06788159999999</v>
+        <v>-30.77696</v>
       </c>
       <c r="O26">
-        <v>-5.813576319999999</v>
+        <v>-6.155391999999999</v>
       </c>
       <c r="P26">
-        <v>-23.25430527999999</v>
+        <v>-24.621568</v>
       </c>
       <c r="Q26">
-        <v>43.54569472</v>
+        <v>42.178432</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1045811626909448</v>
+        <v>0.1053649115268241</v>
       </c>
       <c r="T26">
-        <v>1.115056935263796</v>
+        <v>1.129924361067314</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.05826727043846167</v>
+        <v>0.0559365796209232</v>
       </c>
       <c r="W26">
-        <v>0.2220605776306107</v>
+        <v>0.2226101545253863</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2913363521923084</v>
+        <v>0.279682898104616</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1346762222764646</v>
+        <v>0.1365762222764647</v>
       </c>
       <c r="C27">
-        <v>215.5430574166525</v>
+        <v>201.3249649284557</v>
       </c>
       <c r="D27">
-        <v>369.5430574166525</v>
+        <v>362.5729649284557</v>
       </c>
       <c r="E27">
-        <v>-88</v>
+        <v>-80.75199999999998</v>
       </c>
       <c r="F27">
-        <v>181.2</v>
+        <v>188.448</v>
       </c>
       <c r="G27">
         <v>27.2</v>
@@ -3501,37 +3501,37 @@
         <v>11.95</v>
       </c>
       <c r="M27">
-        <v>42.72696</v>
+        <v>44.4360384</v>
       </c>
       <c r="N27">
-        <v>-30.77696</v>
+        <v>-32.4860384</v>
       </c>
       <c r="O27">
-        <v>-6.155391999999999</v>
+        <v>-6.49720768</v>
       </c>
       <c r="P27">
-        <v>-24.621568</v>
+        <v>-25.98883072</v>
       </c>
       <c r="Q27">
-        <v>42.178432</v>
+        <v>40.81116928</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1053649115268241</v>
+        <v>0.1061698427636731</v>
       </c>
       <c r="T27">
-        <v>1.129924361067314</v>
+        <v>1.145193609189845</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.0559365796209232</v>
+        <v>0.05378517271242615</v>
       </c>
       <c r="W27">
-        <v>0.2226101545253863</v>
+        <v>0.2231174562744099</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.279682898104616</v>
+        <v>0.2689258635621308</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1365762222764647</v>
+        <v>0.1384762222764647</v>
       </c>
       <c r="C28">
-        <v>201.3249649284557</v>
+        <v>187.364936145637</v>
       </c>
       <c r="D28">
-        <v>362.5729649284557</v>
+        <v>355.860936145637</v>
       </c>
       <c r="E28">
-        <v>-80.75199999999998</v>
+        <v>-73.50399999999999</v>
       </c>
       <c r="F28">
-        <v>188.448</v>
+        <v>195.696</v>
       </c>
       <c r="G28">
         <v>27.2</v>
@@ -3583,37 +3583,37 @@
         <v>11.95</v>
       </c>
       <c r="M28">
-        <v>44.4360384</v>
+        <v>46.1451168</v>
       </c>
       <c r="N28">
-        <v>-32.4860384</v>
+        <v>-34.1951168</v>
       </c>
       <c r="O28">
-        <v>-6.49720768</v>
+        <v>-6.839023360000001</v>
       </c>
       <c r="P28">
-        <v>-25.98883072</v>
+        <v>-27.35609344</v>
       </c>
       <c r="Q28">
-        <v>40.81116928</v>
+        <v>39.44390655999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1061698427636731</v>
+        <v>0.1069968269111206</v>
       </c>
       <c r="T28">
-        <v>1.145193609189845</v>
+        <v>1.160881192877377</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.05378517271242615</v>
+        <v>0.05179312927863259</v>
       </c>
       <c r="W28">
-        <v>0.2231174562744099</v>
+        <v>0.2235871801160985</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2689258635621308</v>
+        <v>0.2589656463931629</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1384762222764647</v>
+        <v>0.1403762222764647</v>
       </c>
       <c r="C29">
-        <v>187.364936145637</v>
+        <v>173.6488995701845</v>
       </c>
       <c r="D29">
-        <v>355.860936145637</v>
+        <v>349.3928995701845</v>
       </c>
       <c r="E29">
-        <v>-73.50399999999999</v>
+        <v>-66.25599999999997</v>
       </c>
       <c r="F29">
-        <v>195.696</v>
+        <v>202.944</v>
       </c>
       <c r="G29">
         <v>27.2</v>
@@ -3665,37 +3665,37 @@
         <v>11.95</v>
       </c>
       <c r="M29">
-        <v>46.1451168</v>
+        <v>47.85419520000001</v>
       </c>
       <c r="N29">
-        <v>-34.1951168</v>
+        <v>-35.9041952</v>
       </c>
       <c r="O29">
-        <v>-6.839023360000001</v>
+        <v>-7.180839040000001</v>
       </c>
       <c r="P29">
-        <v>-27.35609344</v>
+        <v>-28.72335616</v>
       </c>
       <c r="Q29">
-        <v>39.44390655999999</v>
+        <v>38.07664384</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1069968269111206</v>
+        <v>0.1078467828404418</v>
       </c>
       <c r="T29">
-        <v>1.160881192877377</v>
+        <v>1.177004542778452</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.05179312927863259</v>
+        <v>0.04994337466153856</v>
       </c>
       <c r="W29">
-        <v>0.2235871801160985</v>
+        <v>0.2240233522548092</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2589656463931629</v>
+        <v>0.2497168733076928</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1403762222764647</v>
+        <v>0.1422762222764646</v>
       </c>
       <c r="C30">
-        <v>173.6488995701845</v>
+        <v>160.1637884811882</v>
       </c>
       <c r="D30">
-        <v>349.3928995701845</v>
+        <v>343.1557884811882</v>
       </c>
       <c r="E30">
-        <v>-66.25599999999997</v>
+        <v>-59.00799999999998</v>
       </c>
       <c r="F30">
-        <v>202.944</v>
+        <v>210.192</v>
       </c>
       <c r="G30">
         <v>27.2</v>
@@ -3747,37 +3747,37 @@
         <v>11.95</v>
       </c>
       <c r="M30">
-        <v>47.85419520000001</v>
+        <v>49.5632736</v>
       </c>
       <c r="N30">
-        <v>-35.9041952</v>
+        <v>-37.6132736</v>
       </c>
       <c r="O30">
-        <v>-7.180839040000001</v>
+        <v>-7.52265472</v>
       </c>
       <c r="P30">
-        <v>-28.72335616</v>
+        <v>-30.09061888</v>
       </c>
       <c r="Q30">
-        <v>38.07664384</v>
+        <v>36.70938112</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1078467828404418</v>
+        <v>0.1087206811903071</v>
       </c>
       <c r="T30">
-        <v>1.177004542778452</v>
+        <v>1.193582071549979</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.04994337466153856</v>
+        <v>0.04822118932838207</v>
       </c>
       <c r="W30">
-        <v>0.2240233522548092</v>
+        <v>0.2244294435563675</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2497168733076928</v>
+        <v>0.2411059466419103</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1422762222764646</v>
+        <v>0.1441762222764646</v>
       </c>
       <c r="C31">
-        <v>160.1637884811882</v>
+        <v>146.8974528249196</v>
       </c>
       <c r="D31">
-        <v>343.1557884811882</v>
+        <v>337.1374528249195</v>
       </c>
       <c r="E31">
-        <v>-59.00800000000001</v>
+        <v>-51.76000000000002</v>
       </c>
       <c r="F31">
-        <v>210.192</v>
+        <v>217.44</v>
       </c>
       <c r="G31">
         <v>27.2</v>
@@ -3829,37 +3829,37 @@
         <v>11.95</v>
       </c>
       <c r="M31">
-        <v>49.5632736</v>
+        <v>51.272352</v>
       </c>
       <c r="N31">
-        <v>-37.61327359999999</v>
+        <v>-39.322352</v>
       </c>
       <c r="O31">
-        <v>-7.522654719999998</v>
+        <v>-7.864470399999999</v>
       </c>
       <c r="P31">
-        <v>-30.09061887999999</v>
+        <v>-31.4578816</v>
       </c>
       <c r="Q31">
-        <v>36.70938112</v>
+        <v>35.3421184</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1087206811903071</v>
+        <v>0.1096195480644544</v>
       </c>
       <c r="T31">
-        <v>1.193582071549979</v>
+        <v>1.210633244000693</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.04822118932838207</v>
+        <v>0.04661381635076933</v>
       </c>
       <c r="W31">
-        <v>0.2244294435563675</v>
+        <v>0.2248084621044886</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2411059466419103</v>
+        <v>0.2330690817538467</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1441762222764646</v>
+        <v>0.1460762222764646</v>
       </c>
       <c r="C32">
-        <v>146.8974528249196</v>
+        <v>133.8385802168422</v>
       </c>
       <c r="D32">
-        <v>337.1374528249195</v>
+        <v>331.3265802168422</v>
       </c>
       <c r="E32">
-        <v>-51.76000000000002</v>
+        <v>-44.512</v>
       </c>
       <c r="F32">
-        <v>217.44</v>
+        <v>224.688</v>
       </c>
       <c r="G32">
         <v>27.2</v>
@@ -3911,37 +3911,37 @@
         <v>11.95</v>
       </c>
       <c r="M32">
-        <v>51.272352</v>
+        <v>52.9814304</v>
       </c>
       <c r="N32">
-        <v>-39.322352</v>
+        <v>-41.0314304</v>
       </c>
       <c r="O32">
-        <v>-7.864470399999999</v>
+        <v>-8.20628608</v>
       </c>
       <c r="P32">
-        <v>-31.4578816</v>
+        <v>-32.82514432</v>
       </c>
       <c r="Q32">
-        <v>35.3421184</v>
+        <v>33.97485568</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1096195480644544</v>
+        <v>0.1105444690508957</v>
       </c>
       <c r="T32">
-        <v>1.210633244000693</v>
+        <v>1.228178653334037</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.04661381635076933</v>
+        <v>0.04511014485558323</v>
       </c>
       <c r="W32">
-        <v>0.2248084621044886</v>
+        <v>0.2251630278430535</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2330690817538467</v>
+        <v>0.2255507242779161</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1460762222764646</v>
+        <v>0.1479762222764646</v>
       </c>
       <c r="C33">
-        <v>133.8385802168422</v>
+        <v>120.9766249748121</v>
       </c>
       <c r="D33">
-        <v>331.3265802168422</v>
+        <v>325.7126249748121</v>
       </c>
       <c r="E33">
-        <v>-44.512</v>
+        <v>-37.26400000000001</v>
       </c>
       <c r="F33">
-        <v>224.688</v>
+        <v>231.936</v>
       </c>
       <c r="G33">
         <v>27.2</v>
@@ -3993,37 +3993,37 @@
         <v>11.95</v>
       </c>
       <c r="M33">
-        <v>52.9814304</v>
+        <v>54.6905088</v>
       </c>
       <c r="N33">
-        <v>-41.0314304</v>
+        <v>-42.74050879999999</v>
       </c>
       <c r="O33">
-        <v>-8.20628608</v>
+        <v>-8.54810176</v>
       </c>
       <c r="P33">
-        <v>-32.82514432</v>
+        <v>-34.19240703999999</v>
       </c>
       <c r="Q33">
-        <v>33.97485568</v>
+        <v>32.60759296000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1105444690508957</v>
+        <v>0.1114965935957619</v>
       </c>
       <c r="T33">
-        <v>1.228178653334037</v>
+        <v>1.246240104118361</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.04511014485558323</v>
+        <v>0.04370045282884625</v>
       </c>
       <c r="W33">
-        <v>0.2251630278430535</v>
+        <v>0.2254954332229581</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2255507242779161</v>
+        <v>0.2185022641442312</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1479762222764646</v>
+        <v>0.1498762222764646</v>
       </c>
       <c r="C34">
-        <v>120.9766249748121</v>
+        <v>108.3017442467854</v>
       </c>
       <c r="D34">
-        <v>325.7126249748121</v>
+        <v>320.2857442467854</v>
       </c>
       <c r="E34">
-        <v>-37.26400000000001</v>
+        <v>-30.01599999999999</v>
       </c>
       <c r="F34">
-        <v>231.936</v>
+        <v>239.184</v>
       </c>
       <c r="G34">
         <v>27.2</v>
@@ -4075,37 +4075,37 @@
         <v>11.95</v>
       </c>
       <c r="M34">
-        <v>54.6905088</v>
+        <v>56.3995872</v>
       </c>
       <c r="N34">
-        <v>-42.74050879999999</v>
+        <v>-44.4495872</v>
       </c>
       <c r="O34">
-        <v>-8.54810176</v>
+        <v>-8.88991744</v>
       </c>
       <c r="P34">
-        <v>-34.19240703999999</v>
+        <v>-35.55966976</v>
       </c>
       <c r="Q34">
-        <v>32.60759296000001</v>
+        <v>31.24033024</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1114965935957619</v>
+        <v>0.1124771397688329</v>
       </c>
       <c r="T34">
-        <v>1.246240104118361</v>
+        <v>1.264840702687291</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.04370045282884625</v>
+        <v>0.04237619668251758</v>
       </c>
       <c r="W34">
-        <v>0.2254954332229581</v>
+        <v>0.2258076928222624</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2185022641442312</v>
+        <v>0.2118809834125879</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1498762222764646</v>
+        <v>0.1517762222764646</v>
       </c>
       <c r="C35">
-        <v>108.3017442467854</v>
+        <v>95.80474041915284</v>
       </c>
       <c r="D35">
-        <v>320.2857442467854</v>
+        <v>315.0367404191529</v>
       </c>
       <c r="E35">
-        <v>-30.01599999999999</v>
+        <v>-22.76799999999997</v>
       </c>
       <c r="F35">
-        <v>239.184</v>
+        <v>246.432</v>
       </c>
       <c r="G35">
         <v>27.2</v>
@@ -4157,37 +4157,37 @@
         <v>11.95</v>
       </c>
       <c r="M35">
-        <v>56.3995872</v>
+        <v>58.10866560000001</v>
       </c>
       <c r="N35">
-        <v>-44.4495872</v>
+        <v>-46.15866560000001</v>
       </c>
       <c r="O35">
-        <v>-8.88991744</v>
+        <v>-9.231733120000001</v>
       </c>
       <c r="P35">
-        <v>-35.55966976</v>
+        <v>-36.92693248</v>
       </c>
       <c r="Q35">
-        <v>31.24033024</v>
+        <v>29.87306751999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1124771397688329</v>
+        <v>0.1134873994623001</v>
       </c>
       <c r="T35">
-        <v>1.264840702687291</v>
+        <v>1.284004955758311</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.04237619668251758</v>
+        <v>0.04112983795656117</v>
       </c>
       <c r="W35">
-        <v>0.2258076928222624</v>
+        <v>0.2261015842098429</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2118809834125879</v>
+        <v>0.2056491897828059</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1517762222764646</v>
+        <v>0.1536762222764647</v>
       </c>
       <c r="C36">
-        <v>95.80474041915284</v>
+        <v>83.47700909680867</v>
       </c>
       <c r="D36">
-        <v>315.0367404191529</v>
+        <v>309.9570090968087</v>
       </c>
       <c r="E36">
-        <v>-22.76799999999997</v>
+        <v>-15.51999999999998</v>
       </c>
       <c r="F36">
-        <v>246.432</v>
+        <v>253.68</v>
       </c>
       <c r="G36">
         <v>27.2</v>
@@ -4239,37 +4239,37 @@
         <v>11.95</v>
       </c>
       <c r="M36">
-        <v>58.10866560000001</v>
+        <v>59.817744</v>
       </c>
       <c r="N36">
-        <v>-46.15866560000001</v>
+        <v>-47.867744</v>
       </c>
       <c r="O36">
-        <v>-9.231733120000001</v>
+        <v>-9.573548800000001</v>
       </c>
       <c r="P36">
-        <v>-36.92693248</v>
+        <v>-38.2941952</v>
       </c>
       <c r="Q36">
-        <v>29.87306751999999</v>
+        <v>28.50580479999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1134873994623001</v>
+        <v>0.1145287440694124</v>
       </c>
       <c r="T36">
-        <v>1.284004955758311</v>
+        <v>1.303758878154593</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.04112983795656117</v>
+        <v>0.03995469972923085</v>
       </c>
       <c r="W36">
-        <v>0.2261015842098429</v>
+        <v>0.2263786818038474</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2056491897828059</v>
+        <v>0.1997734986461542</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1536762222764647</v>
+        <v>0.1555762222764646</v>
       </c>
       <c r="C37">
-        <v>83.47700909680867</v>
+        <v>71.31049203605403</v>
       </c>
       <c r="D37">
-        <v>309.9570090968087</v>
+        <v>305.038492036054</v>
       </c>
       <c r="E37">
-        <v>-15.51999999999998</v>
+        <v>-8.271999999999991</v>
       </c>
       <c r="F37">
-        <v>253.68</v>
+        <v>260.928</v>
       </c>
       <c r="G37">
         <v>27.2</v>
@@ -4321,37 +4321,37 @@
         <v>11.95</v>
       </c>
       <c r="M37">
-        <v>59.817744</v>
+        <v>61.5268224</v>
       </c>
       <c r="N37">
-        <v>-47.867744</v>
+        <v>-49.5768224</v>
       </c>
       <c r="O37">
-        <v>-9.573548800000001</v>
+        <v>-9.915364480000001</v>
       </c>
       <c r="P37">
-        <v>-38.2941952</v>
+        <v>-39.66145792</v>
       </c>
       <c r="Q37">
-        <v>28.50580479999999</v>
+        <v>27.13854208</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1145287440694124</v>
+        <v>0.115602630695497</v>
       </c>
       <c r="T37">
-        <v>1.303758878154593</v>
+        <v>1.324130110625758</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03995469972923085</v>
+        <v>0.03884484695897444</v>
       </c>
       <c r="W37">
-        <v>0.2263786818038474</v>
+        <v>0.2266403850870738</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1997734986461542</v>
+        <v>0.1942242347948722</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1555762222764646</v>
+        <v>0.1574762222764647</v>
       </c>
       <c r="C38">
-        <v>71.31049203605403</v>
+        <v>59.29763448877208</v>
       </c>
       <c r="D38">
-        <v>305.038492036054</v>
+        <v>300.2736344887721</v>
       </c>
       <c r="E38">
-        <v>-8.271999999999991</v>
+        <v>-1.024000000000001</v>
       </c>
       <c r="F38">
-        <v>260.928</v>
+        <v>268.176</v>
       </c>
       <c r="G38">
         <v>27.2</v>
@@ -4403,37 +4403,37 @@
         <v>11.95</v>
       </c>
       <c r="M38">
-        <v>61.5268224</v>
+        <v>63.2359008</v>
       </c>
       <c r="N38">
-        <v>-49.5768224</v>
+        <v>-51.2859008</v>
       </c>
       <c r="O38">
-        <v>-9.915364480000001</v>
+        <v>-10.25718016</v>
       </c>
       <c r="P38">
-        <v>-39.66145792</v>
+        <v>-41.02872064</v>
       </c>
       <c r="Q38">
-        <v>27.13854208</v>
+        <v>25.77127935999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.115602630695497</v>
+        <v>0.1167106089605049</v>
       </c>
       <c r="T38">
-        <v>1.324130110625758</v>
+        <v>1.345148048889659</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03884484695897444</v>
+        <v>0.03779498623035352</v>
       </c>
       <c r="W38">
-        <v>0.2266403850870738</v>
+        <v>0.2268879422468827</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1942242347948722</v>
+        <v>0.1889749311517676</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1574762222764647</v>
+        <v>0.1593762222764646</v>
       </c>
       <c r="C39">
-        <v>59.29763448877208</v>
+        <v>47.43134648295216</v>
       </c>
       <c r="D39">
-        <v>300.2736344887721</v>
+        <v>295.6553464829522</v>
       </c>
       <c r="E39">
-        <v>-1.024000000000001</v>
+        <v>6.22399999999999</v>
       </c>
       <c r="F39">
-        <v>268.176</v>
+        <v>275.424</v>
       </c>
       <c r="G39">
         <v>27.2</v>
@@ -4485,37 +4485,37 @@
         <v>11.95</v>
       </c>
       <c r="M39">
-        <v>63.2359008</v>
+        <v>64.94497919999999</v>
       </c>
       <c r="N39">
-        <v>-51.2859008</v>
+        <v>-52.99497919999999</v>
       </c>
       <c r="O39">
-        <v>-10.25718016</v>
+        <v>-10.59899584</v>
       </c>
       <c r="P39">
-        <v>-41.02872064</v>
+        <v>-42.39598335999999</v>
       </c>
       <c r="Q39">
-        <v>25.77127935999999</v>
+        <v>24.40401664000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1167106089605049</v>
+        <v>0.1178543284598678</v>
       </c>
       <c r="T39">
-        <v>1.345148048889659</v>
+        <v>1.366843985162073</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03779498623035352</v>
+        <v>0.03680038132955474</v>
       </c>
       <c r="W39">
-        <v>0.2268879422468827</v>
+        <v>0.227122470082491</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1889749311517676</v>
+        <v>0.1840019066477737</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1593762222764646</v>
+        <v>0.1612762222764647</v>
       </c>
       <c r="C40">
-        <v>47.43134648295216</v>
+        <v>35.70496762218397</v>
       </c>
       <c r="D40">
-        <v>295.6553464829522</v>
+        <v>291.176967622184</v>
       </c>
       <c r="E40">
-        <v>6.22399999999999</v>
+        <v>13.47199999999998</v>
       </c>
       <c r="F40">
-        <v>275.424</v>
+        <v>282.672</v>
       </c>
       <c r="G40">
         <v>27.2</v>
@@ -4567,37 +4567,37 @@
         <v>11.95</v>
       </c>
       <c r="M40">
-        <v>64.94497919999999</v>
+        <v>66.6540576</v>
       </c>
       <c r="N40">
-        <v>-52.99497919999999</v>
+        <v>-54.7040576</v>
       </c>
       <c r="O40">
-        <v>-10.59899584</v>
+        <v>-10.94081152</v>
       </c>
       <c r="P40">
-        <v>-42.39598335999999</v>
+        <v>-43.76324608</v>
       </c>
       <c r="Q40">
-        <v>24.40401664000001</v>
+        <v>23.03675392</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1178543284598678</v>
+        <v>0.11903554695921</v>
       </c>
       <c r="T40">
-        <v>1.366843985162073</v>
+        <v>1.389251263607353</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03680038132955474</v>
+        <v>0.0358567818082841</v>
       </c>
       <c r="W40">
-        <v>0.227122470082491</v>
+        <v>0.2273449708496066</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1840019066477737</v>
+        <v>0.1792839090414204</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1612762222764647</v>
+        <v>0.1631762222764647</v>
       </c>
       <c r="C41">
-        <v>35.70496762218397</v>
+        <v>24.11223503657249</v>
       </c>
       <c r="D41">
-        <v>291.176967622184</v>
+        <v>286.8322350365725</v>
       </c>
       <c r="E41">
-        <v>13.47199999999998</v>
+        <v>20.72000000000003</v>
       </c>
       <c r="F41">
-        <v>282.672</v>
+        <v>289.92</v>
       </c>
       <c r="G41">
         <v>27.2</v>
@@ -4649,37 +4649,37 @@
         <v>11.95</v>
       </c>
       <c r="M41">
-        <v>66.6540576</v>
+        <v>68.36313600000001</v>
       </c>
       <c r="N41">
-        <v>-54.7040576</v>
+        <v>-56.41313600000001</v>
       </c>
       <c r="O41">
-        <v>-10.94081152</v>
+        <v>-11.2826272</v>
       </c>
       <c r="P41">
-        <v>-43.76324608</v>
+        <v>-45.13050880000001</v>
       </c>
       <c r="Q41">
-        <v>23.03675392</v>
+        <v>21.66949119999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.11903554695921</v>
+        <v>0.1202561394085301</v>
       </c>
       <c r="T41">
-        <v>1.389251263607353</v>
+        <v>1.412405451334142</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.0358567818082841</v>
+        <v>0.03496036226307699</v>
       </c>
       <c r="W41">
-        <v>0.2273449708496066</v>
+        <v>0.2275563465783665</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1792839090414204</v>
+        <v>0.174801811315385</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1631762222764647</v>
+        <v>0.1650762222764646</v>
       </c>
       <c r="C42">
-        <v>24.11223503657249</v>
+        <v>12.64725416074901</v>
       </c>
       <c r="D42">
-        <v>286.8322350365725</v>
+        <v>282.615254160749</v>
       </c>
       <c r="E42">
-        <v>20.72000000000003</v>
+        <v>27.96800000000002</v>
       </c>
       <c r="F42">
-        <v>289.92</v>
+        <v>297.168</v>
       </c>
       <c r="G42">
         <v>27.2</v>
@@ -4731,37 +4731,37 @@
         <v>11.95</v>
       </c>
       <c r="M42">
-        <v>68.36313600000001</v>
+        <v>70.07221440000001</v>
       </c>
       <c r="N42">
-        <v>-56.41313600000001</v>
+        <v>-58.1222144</v>
       </c>
       <c r="O42">
-        <v>-11.2826272</v>
+        <v>-11.62444288</v>
       </c>
       <c r="P42">
-        <v>-45.13050880000001</v>
+        <v>-46.49777152</v>
       </c>
       <c r="Q42">
-        <v>21.66949119999999</v>
+        <v>20.30222848</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1202561394085301</v>
+        <v>0.1215181078730815</v>
       </c>
       <c r="T42">
-        <v>1.412405451334142</v>
+        <v>1.436344526780484</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.03496036226307699</v>
+        <v>0.03410767050056292</v>
       </c>
       <c r="W42">
-        <v>0.2275563465783665</v>
+        <v>0.2277574112959673</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.174801811315385</v>
+        <v>0.1705383525028146</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1650762222764646</v>
+        <v>0.1669762222764646</v>
       </c>
       <c r="C43">
-        <v>12.64725416074901</v>
+        <v>1.304472052246012</v>
       </c>
       <c r="D43">
-        <v>282.615254160749</v>
+        <v>278.520472052246</v>
       </c>
       <c r="E43">
-        <v>27.96800000000002</v>
+        <v>35.21600000000001</v>
       </c>
       <c r="F43">
-        <v>297.168</v>
+        <v>304.416</v>
       </c>
       <c r="G43">
         <v>27.2</v>
@@ -4813,37 +4813,37 @@
         <v>11.95</v>
       </c>
       <c r="M43">
-        <v>70.07221440000001</v>
+        <v>71.7812928</v>
       </c>
       <c r="N43">
-        <v>-58.1222144</v>
+        <v>-59.8312928</v>
       </c>
       <c r="O43">
-        <v>-11.62444288</v>
+        <v>-11.96625856</v>
       </c>
       <c r="P43">
-        <v>-46.49777152</v>
+        <v>-47.86503424</v>
       </c>
       <c r="Q43">
-        <v>20.30222848</v>
+        <v>18.93496576</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1215181078730815</v>
+        <v>0.1228235924915829</v>
       </c>
       <c r="T43">
-        <v>1.436344526780484</v>
+        <v>1.461109087587044</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03410767050056292</v>
+        <v>0.03329558310769238</v>
       </c>
       <c r="W43">
-        <v>0.2277574112959673</v>
+        <v>0.2279489015032061</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1705383525028146</v>
+        <v>0.1664779155384619</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1669762222764646</v>
+        <v>0.1688762222764646</v>
       </c>
       <c r="C44">
-        <v>1.304472052246012</v>
+        <v>-9.92134700372975</v>
       </c>
       <c r="D44">
-        <v>278.520472052246</v>
+        <v>274.5426529962702</v>
       </c>
       <c r="E44">
-        <v>35.21600000000001</v>
+        <v>42.464</v>
       </c>
       <c r="F44">
-        <v>304.416</v>
+        <v>311.664</v>
       </c>
       <c r="G44">
         <v>27.2</v>
@@ -4895,37 +4895,37 @@
         <v>11.95</v>
       </c>
       <c r="M44">
-        <v>71.7812928</v>
+        <v>73.4903712</v>
       </c>
       <c r="N44">
-        <v>-59.8312928</v>
+        <v>-61.5403712</v>
       </c>
       <c r="O44">
-        <v>-11.96625856</v>
+        <v>-12.30807424</v>
       </c>
       <c r="P44">
-        <v>-47.86503424</v>
+        <v>-49.23229696</v>
       </c>
       <c r="Q44">
-        <v>18.93496576</v>
+        <v>17.56770304</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1228235924915829</v>
+        <v>0.1241748835879264</v>
       </c>
       <c r="T44">
-        <v>1.461109087587043</v>
+        <v>1.486742580351728</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03329558310769238</v>
+        <v>0.03252126722146698</v>
       </c>
       <c r="W44">
-        <v>0.2279489015032061</v>
+        <v>0.2281314851891781</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1664779155384619</v>
+        <v>0.1626063361073349</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1688762222764646</v>
+        <v>0.1707762222764647</v>
       </c>
       <c r="C45">
-        <v>-9.92134700372975</v>
+        <v>-21.03514382849124</v>
       </c>
       <c r="D45">
-        <v>274.5426529962702</v>
+        <v>270.6768561715087</v>
       </c>
       <c r="E45">
-        <v>42.464</v>
+        <v>49.71199999999999</v>
       </c>
       <c r="F45">
-        <v>311.664</v>
+        <v>318.912</v>
       </c>
       <c r="G45">
         <v>27.2</v>
@@ -4977,37 +4977,37 @@
         <v>11.95</v>
       </c>
       <c r="M45">
-        <v>73.4903712</v>
+        <v>75.19944959999999</v>
       </c>
       <c r="N45">
-        <v>-61.5403712</v>
+        <v>-63.24944959999999</v>
       </c>
       <c r="O45">
-        <v>-12.30807424</v>
+        <v>-12.64988992</v>
       </c>
       <c r="P45">
-        <v>-49.23229696</v>
+        <v>-50.59955967999999</v>
       </c>
       <c r="Q45">
-        <v>17.56770304</v>
+        <v>16.20044032000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1241748835879264</v>
+        <v>0.125574435080568</v>
       </c>
       <c r="T45">
-        <v>1.486742580351728</v>
+        <v>1.513291555000867</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03252126722146698</v>
+        <v>0.03178214751188818</v>
       </c>
       <c r="W45">
-        <v>0.2281314851891781</v>
+        <v>0.2283057696166968</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1626063361073349</v>
+        <v>0.158910737559441</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1707762222764647</v>
+        <v>0.1726762222764646</v>
       </c>
       <c r="C46">
-        <v>-21.03514382849124</v>
+        <v>-32.04158482335646</v>
       </c>
       <c r="D46">
-        <v>270.6768561715087</v>
+        <v>266.9184151766435</v>
       </c>
       <c r="E46">
-        <v>49.71199999999999</v>
+        <v>56.95999999999998</v>
       </c>
       <c r="F46">
-        <v>318.912</v>
+        <v>326.16</v>
       </c>
       <c r="G46">
         <v>27.2</v>
@@ -5059,37 +5059,37 @@
         <v>11.95</v>
       </c>
       <c r="M46">
-        <v>75.19944959999999</v>
+        <v>76.90852799999999</v>
       </c>
       <c r="N46">
-        <v>-63.24944959999999</v>
+        <v>-64.95852799999999</v>
       </c>
       <c r="O46">
-        <v>-12.64988992</v>
+        <v>-12.9917056</v>
       </c>
       <c r="P46">
-        <v>-50.59955967999999</v>
+        <v>-51.96682239999999</v>
       </c>
       <c r="Q46">
-        <v>16.20044032000001</v>
+        <v>14.83317760000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.125574435080568</v>
+        <v>0.1270248793547601</v>
       </c>
       <c r="T46">
-        <v>1.513291555000867</v>
+        <v>1.540805946909973</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03178214751188818</v>
+        <v>0.03107587756717956</v>
       </c>
       <c r="W46">
-        <v>0.2283057696166968</v>
+        <v>0.2284723080696591</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.158910737559441</v>
+        <v>0.1553793878358978</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1726762222764646</v>
+        <v>0.1745762222764646</v>
       </c>
       <c r="C47">
-        <v>-32.04158482335646</v>
+        <v>-42.94508076080564</v>
       </c>
       <c r="D47">
-        <v>266.9184151766435</v>
+        <v>263.2629192391944</v>
       </c>
       <c r="E47">
-        <v>56.95999999999998</v>
+        <v>64.20800000000003</v>
       </c>
       <c r="F47">
-        <v>326.16</v>
+        <v>333.408</v>
       </c>
       <c r="G47">
         <v>27.2</v>
@@ -5141,37 +5141,37 @@
         <v>11.95</v>
       </c>
       <c r="M47">
-        <v>76.90852799999999</v>
+        <v>78.61760640000001</v>
       </c>
       <c r="N47">
-        <v>-64.95852799999999</v>
+        <v>-66.66760640000001</v>
       </c>
       <c r="O47">
-        <v>-12.9917056</v>
+        <v>-13.33352128</v>
       </c>
       <c r="P47">
-        <v>-51.96682239999999</v>
+        <v>-53.33408512000001</v>
       </c>
       <c r="Q47">
-        <v>14.83317760000001</v>
+        <v>13.46591487999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1270248793547601</v>
+        <v>0.1285290437872557</v>
       </c>
       <c r="T47">
-        <v>1.540805946909973</v>
+        <v>1.569339390371269</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03107587756717956</v>
+        <v>0.0304003150113713</v>
       </c>
       <c r="W47">
-        <v>0.2284723080696591</v>
+        <v>0.2286316057203187</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1553793878358978</v>
+        <v>0.1520015750568565</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1745762222764646</v>
+        <v>0.1764762222764647</v>
       </c>
       <c r="C48">
-        <v>-42.94508076080564</v>
+        <v>-53.74980405240984</v>
       </c>
       <c r="D48">
-        <v>263.2629192391944</v>
+        <v>259.7061959475902</v>
       </c>
       <c r="E48">
-        <v>64.20800000000003</v>
+        <v>71.45600000000002</v>
       </c>
       <c r="F48">
-        <v>333.408</v>
+        <v>340.656</v>
       </c>
       <c r="G48">
         <v>27.2</v>
@@ -5223,37 +5223,37 @@
         <v>11.95</v>
       </c>
       <c r="M48">
-        <v>78.61760640000001</v>
+        <v>80.32668480000001</v>
       </c>
       <c r="N48">
-        <v>-66.66760640000001</v>
+        <v>-68.37668480000001</v>
       </c>
       <c r="O48">
-        <v>-13.33352128</v>
+        <v>-13.67533696</v>
       </c>
       <c r="P48">
-        <v>-53.33408512000001</v>
+        <v>-54.70134784</v>
       </c>
       <c r="Q48">
-        <v>13.46591487999999</v>
+        <v>12.09865215999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1285290437872557</v>
+        <v>0.1300899691417322</v>
       </c>
       <c r="T48">
-        <v>1.569339390371269</v>
+        <v>1.598949567548086</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.0304003150113713</v>
+        <v>0.0297534997983634</v>
       </c>
       <c r="W48">
-        <v>0.2286316057203187</v>
+        <v>0.2287841247475459</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1520015750568565</v>
+        <v>0.148767498991817</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1764762222764647</v>
+        <v>0.1783762222764647</v>
       </c>
       <c r="C49">
-        <v>-53.74980405240984</v>
+        <v>-64.45970463566249</v>
       </c>
       <c r="D49">
-        <v>259.7061959475902</v>
+        <v>256.2442953643375</v>
       </c>
       <c r="E49">
-        <v>71.45600000000002</v>
+        <v>78.70400000000001</v>
       </c>
       <c r="F49">
-        <v>340.656</v>
+        <v>347.904</v>
       </c>
       <c r="G49">
         <v>27.2</v>
@@ -5305,37 +5305,37 @@
         <v>11.95</v>
       </c>
       <c r="M49">
-        <v>80.32668480000001</v>
+        <v>82.03576320000001</v>
       </c>
       <c r="N49">
-        <v>-68.37668480000001</v>
+        <v>-70.0857632</v>
       </c>
       <c r="O49">
-        <v>-13.67533696</v>
+        <v>-14.01715264</v>
       </c>
       <c r="P49">
-        <v>-54.70134784</v>
+        <v>-56.06861056</v>
       </c>
       <c r="Q49">
-        <v>12.09865215999999</v>
+        <v>10.73138943999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1300899691417322</v>
+        <v>0.1317109300867655</v>
       </c>
       <c r="T49">
-        <v>1.598949567548086</v>
+        <v>1.629698597693241</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0297534997983634</v>
+        <v>0.02913363521923083</v>
       </c>
       <c r="W49">
-        <v>0.2287841247475459</v>
+        <v>0.2289302888153054</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.148767498991817</v>
+        <v>0.1456681760961541</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1783762222764646</v>
+        <v>0.1802762222764646</v>
       </c>
       <c r="C50">
-        <v>-64.45970463566255</v>
+        <v>-75.0785246068935</v>
       </c>
       <c r="D50">
-        <v>256.2442953643374</v>
+        <v>252.8734753931065</v>
       </c>
       <c r="E50">
-        <v>78.70399999999995</v>
+        <v>85.952</v>
       </c>
       <c r="F50">
-        <v>347.9039999999999</v>
+        <v>355.152</v>
       </c>
       <c r="G50">
         <v>27.2</v>
@@ -5387,37 +5387,37 @@
         <v>11.95</v>
       </c>
       <c r="M50">
-        <v>82.03576319999999</v>
+        <v>83.7448416</v>
       </c>
       <c r="N50">
-        <v>-70.08576319999999</v>
+        <v>-71.7948416</v>
       </c>
       <c r="O50">
-        <v>-14.01715264</v>
+        <v>-14.35896832</v>
       </c>
       <c r="P50">
-        <v>-56.06861055999999</v>
+        <v>-57.43587328</v>
       </c>
       <c r="Q50">
-        <v>10.73138944000001</v>
+        <v>9.364126720000002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1317109300867655</v>
+        <v>0.1333954581276825</v>
       </c>
       <c r="T50">
-        <v>1.629698597693241</v>
+        <v>1.661653472157814</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02913363521923084</v>
+        <v>0.0285390712351649</v>
       </c>
       <c r="W50">
-        <v>0.2289302888153054</v>
+        <v>0.2290704870027481</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1456681760961541</v>
+        <v>0.1426953561758245</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1802762222764646</v>
+        <v>0.1821762222764646</v>
       </c>
       <c r="C51">
-        <v>-75.0785246068935</v>
+        <v>-85.60981171422492</v>
       </c>
       <c r="D51">
-        <v>252.8734753931065</v>
+        <v>249.590188285775</v>
       </c>
       <c r="E51">
-        <v>85.952</v>
+        <v>93.19999999999999</v>
       </c>
       <c r="F51">
-        <v>355.152</v>
+        <v>362.4</v>
       </c>
       <c r="G51">
         <v>27.2</v>
@@ -5469,37 +5469,37 @@
         <v>11.95</v>
       </c>
       <c r="M51">
-        <v>83.7448416</v>
+        <v>85.45392</v>
       </c>
       <c r="N51">
-        <v>-71.7948416</v>
+        <v>-73.50391999999999</v>
       </c>
       <c r="O51">
-        <v>-14.35896832</v>
+        <v>-14.700784</v>
       </c>
       <c r="P51">
-        <v>-57.43587328</v>
+        <v>-58.80313599999999</v>
       </c>
       <c r="Q51">
-        <v>9.364126720000002</v>
+        <v>7.996864000000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1333954581276825</v>
+        <v>0.1351473672902361</v>
       </c>
       <c r="T51">
-        <v>1.661653472157814</v>
+        <v>1.694886541600971</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.0285390712351649</v>
+        <v>0.0279682898104616</v>
       </c>
       <c r="W51">
-        <v>0.2290704870027481</v>
+        <v>0.2292050772626932</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1426953561758245</v>
+        <v>0.139841449052308</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1821762222764646</v>
+        <v>0.1840762222764646</v>
       </c>
       <c r="C52">
-        <v>-85.60981171422492</v>
+        <v>-96.05693181285494</v>
       </c>
       <c r="D52">
-        <v>249.590188285775</v>
+        <v>246.391068187145</v>
       </c>
       <c r="E52">
-        <v>93.19999999999999</v>
+        <v>100.448</v>
       </c>
       <c r="F52">
-        <v>362.4</v>
+        <v>369.648</v>
       </c>
       <c r="G52">
         <v>27.2</v>
@@ -5551,37 +5551,37 @@
         <v>11.95</v>
       </c>
       <c r="M52">
-        <v>85.45392</v>
+        <v>87.16299839999999</v>
       </c>
       <c r="N52">
-        <v>-73.50391999999999</v>
+        <v>-75.21299839999999</v>
       </c>
       <c r="O52">
-        <v>-14.700784</v>
+        <v>-15.04259968</v>
       </c>
       <c r="P52">
-        <v>-58.80313599999999</v>
+        <v>-60.17039871999999</v>
       </c>
       <c r="Q52">
-        <v>7.996864000000002</v>
+        <v>6.629601280000003</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1351473672902361</v>
+        <v>0.1369707829492205</v>
       </c>
       <c r="T52">
-        <v>1.694886541600971</v>
+        <v>1.729476062858133</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0279682898104616</v>
+        <v>0.02741989197104078</v>
       </c>
       <c r="W52">
-        <v>0.2292050772626932</v>
+        <v>0.2293343894732286</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.139841449052308</v>
+        <v>0.1370994598552039</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1840762222764646</v>
+        <v>0.1859762222764647</v>
       </c>
       <c r="C53">
-        <v>-96.05693181285494</v>
+        <v>-106.4230803745884</v>
       </c>
       <c r="D53">
-        <v>246.391068187145</v>
+        <v>243.2729196254116</v>
       </c>
       <c r="E53">
-        <v>100.448</v>
+        <v>107.696</v>
       </c>
       <c r="F53">
-        <v>369.648</v>
+        <v>376.896</v>
       </c>
       <c r="G53">
         <v>27.2</v>
@@ -5633,37 +5633,37 @@
         <v>11.95</v>
       </c>
       <c r="M53">
-        <v>87.16299839999999</v>
+        <v>88.8720768</v>
       </c>
       <c r="N53">
-        <v>-75.21299839999999</v>
+        <v>-76.9220768</v>
       </c>
       <c r="O53">
-        <v>-15.04259968</v>
+        <v>-15.38441536</v>
       </c>
       <c r="P53">
-        <v>-60.17039871999999</v>
+        <v>-61.53766144</v>
       </c>
       <c r="Q53">
-        <v>6.629601280000003</v>
+        <v>5.262338559999996</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1369707829492205</v>
+        <v>0.1388701742606626</v>
       </c>
       <c r="T53">
-        <v>1.729476062858133</v>
+        <v>1.765506814167678</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02741989197104078</v>
+        <v>0.02689258635621307</v>
       </c>
       <c r="W53">
-        <v>0.2293343894732286</v>
+        <v>0.229458728137205</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1370994598552039</v>
+        <v>0.1344629317810654</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1859762222764647</v>
+        <v>0.1878762222764647</v>
       </c>
       <c r="C54">
-        <v>-106.4230803745884</v>
+        <v>-116.7112931343524</v>
       </c>
       <c r="D54">
-        <v>243.2729196254116</v>
+        <v>240.2327068656476</v>
       </c>
       <c r="E54">
-        <v>107.696</v>
+        <v>114.944</v>
       </c>
       <c r="F54">
-        <v>376.896</v>
+        <v>384.144</v>
       </c>
       <c r="G54">
         <v>27.2</v>
@@ -5715,37 +5715,37 @@
         <v>11.95</v>
       </c>
       <c r="M54">
-        <v>88.8720768</v>
+        <v>90.58115520000001</v>
       </c>
       <c r="N54">
-        <v>-76.9220768</v>
+        <v>-78.63115520000001</v>
       </c>
       <c r="O54">
-        <v>-15.38441536</v>
+        <v>-15.72623104</v>
       </c>
       <c r="P54">
-        <v>-61.53766144</v>
+        <v>-62.90492416000001</v>
       </c>
       <c r="Q54">
-        <v>5.262338559999996</v>
+        <v>3.89507583999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1388701742606626</v>
+        <v>0.1408503907342938</v>
       </c>
       <c r="T54">
-        <v>1.765506814167678</v>
+        <v>1.803070788937203</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02689258635621307</v>
+        <v>0.0263851790664732</v>
       </c>
       <c r="W54">
-        <v>0.229458728137205</v>
+        <v>0.2295783747761256</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1344629317810654</v>
+        <v>0.131925895332366</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1878762222764647</v>
+        <v>0.1897762222764647</v>
       </c>
       <c r="C55">
-        <v>-116.7112931343524</v>
+        <v>-126.9244559482599</v>
       </c>
       <c r="D55">
-        <v>240.2327068656476</v>
+        <v>237.2675440517401</v>
       </c>
       <c r="E55">
-        <v>114.944</v>
+        <v>122.192</v>
       </c>
       <c r="F55">
-        <v>384.144</v>
+        <v>391.392</v>
       </c>
       <c r="G55">
         <v>27.2</v>
@@ -5797,37 +5797,37 @@
         <v>11.95</v>
       </c>
       <c r="M55">
-        <v>90.58115520000001</v>
+        <v>92.29023360000001</v>
       </c>
       <c r="N55">
-        <v>-78.63115520000001</v>
+        <v>-80.3402336</v>
       </c>
       <c r="O55">
-        <v>-15.72623104</v>
+        <v>-16.06804672</v>
       </c>
       <c r="P55">
-        <v>-62.90492416000001</v>
+        <v>-64.27218688000001</v>
       </c>
       <c r="Q55">
-        <v>3.89507583999999</v>
+        <v>2.52781311999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1408503907342938</v>
+        <v>0.1429167035763436</v>
       </c>
       <c r="T55">
-        <v>1.803070788937203</v>
+        <v>1.842267980001055</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0263851790664732</v>
+        <v>0.02589656463931629</v>
       </c>
       <c r="W55">
-        <v>0.2295783747761256</v>
+        <v>0.2296935900580492</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.131925895332366</v>
+        <v>0.1294828231965814</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1897762222764647</v>
+        <v>0.1916762222764646</v>
       </c>
       <c r="C56">
-        <v>-126.9244559482599</v>
+        <v>-137.0653139305125</v>
       </c>
       <c r="D56">
-        <v>237.2675440517401</v>
+        <v>234.3746860694875</v>
       </c>
       <c r="E56">
-        <v>122.192</v>
+        <v>129.44</v>
       </c>
       <c r="F56">
-        <v>391.392</v>
+        <v>398.64</v>
       </c>
       <c r="G56">
         <v>27.2</v>
@@ -5879,37 +5879,37 @@
         <v>11.95</v>
       </c>
       <c r="M56">
-        <v>92.29023360000001</v>
+        <v>93.999312</v>
       </c>
       <c r="N56">
-        <v>-80.3402336</v>
+        <v>-82.049312</v>
       </c>
       <c r="O56">
-        <v>-16.06804672</v>
+        <v>-16.4098624</v>
       </c>
       <c r="P56">
-        <v>-64.27218688000001</v>
+        <v>-65.63944960000001</v>
       </c>
       <c r="Q56">
-        <v>2.52781311999999</v>
+        <v>1.160550399999991</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1429167035763436</v>
+        <v>0.1450748525447068</v>
       </c>
       <c r="T56">
-        <v>1.842267980001055</v>
+        <v>1.883207268445523</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02589656463931629</v>
+        <v>0.02542571800951055</v>
       </c>
       <c r="W56">
-        <v>0.2296935900580492</v>
+        <v>0.2298046156933574</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1294828231965814</v>
+        <v>0.1271285900475527</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1916762222764646</v>
+        <v>0.1935762222764646</v>
       </c>
       <c r="C57">
-        <v>-137.0653139305125</v>
+        <v>-147.1364799299521</v>
       </c>
       <c r="D57">
-        <v>234.3746860694875</v>
+        <v>231.5515200700479</v>
       </c>
       <c r="E57">
-        <v>129.44</v>
+        <v>136.688</v>
       </c>
       <c r="F57">
-        <v>398.64</v>
+        <v>405.888</v>
       </c>
       <c r="G57">
         <v>27.2</v>
@@ -5961,37 +5961,37 @@
         <v>11.95</v>
       </c>
       <c r="M57">
-        <v>93.999312</v>
+        <v>95.70839040000001</v>
       </c>
       <c r="N57">
-        <v>-82.049312</v>
+        <v>-83.75839040000001</v>
       </c>
       <c r="O57">
-        <v>-16.4098624</v>
+        <v>-16.75167808</v>
       </c>
       <c r="P57">
-        <v>-65.63944960000001</v>
+        <v>-67.00671232000001</v>
       </c>
       <c r="Q57">
-        <v>1.160550399999991</v>
+        <v>-0.2067123200000083</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1450748525447068</v>
+        <v>0.1473310991934501</v>
       </c>
       <c r="T57">
-        <v>1.883207268445523</v>
+        <v>1.926007433637467</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02542571800951055</v>
+        <v>0.02497168733076928</v>
       </c>
       <c r="W57">
-        <v>0.2298046156933574</v>
+        <v>0.2299116761274046</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1271285900475527</v>
+        <v>0.1248584366538464</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1935762222764646</v>
+        <v>0.1954762222764647</v>
       </c>
       <c r="C58">
-        <v>-147.1364799299521</v>
+        <v>-157.1404424012748</v>
       </c>
       <c r="D58">
-        <v>231.5515200700479</v>
+        <v>228.7955575987253</v>
       </c>
       <c r="E58">
-        <v>136.688</v>
+        <v>143.936</v>
       </c>
       <c r="F58">
-        <v>405.888</v>
+        <v>413.136</v>
       </c>
       <c r="G58">
         <v>27.2</v>
@@ -6043,37 +6043,37 @@
         <v>11.95</v>
       </c>
       <c r="M58">
-        <v>95.70839040000001</v>
+        <v>97.41746880000001</v>
       </c>
       <c r="N58">
-        <v>-83.75839040000001</v>
+        <v>-85.46746880000001</v>
       </c>
       <c r="O58">
-        <v>-16.75167808</v>
+        <v>-17.09349376</v>
       </c>
       <c r="P58">
-        <v>-67.00671232000001</v>
+        <v>-68.37397504</v>
       </c>
       <c r="Q58">
-        <v>-0.2067123200000083</v>
+        <v>-1.573975040000008</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1473310991934501</v>
+        <v>0.1496922875467862</v>
       </c>
       <c r="T58">
-        <v>1.926007433637467</v>
+        <v>1.970798304187175</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02497168733076928</v>
+        <v>0.02453358755303649</v>
       </c>
       <c r="W58">
-        <v>0.2299116761274046</v>
+        <v>0.230014980054994</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1248584366538464</v>
+        <v>0.1226679377651825</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1954762222764647</v>
+        <v>0.1973762222764647</v>
       </c>
       <c r="C59">
-        <v>-157.1404424012748</v>
+        <v>-167.0795727207519</v>
       </c>
       <c r="D59">
-        <v>228.7955575987253</v>
+        <v>226.1044272792482</v>
       </c>
       <c r="E59">
-        <v>143.936</v>
+        <v>151.184</v>
       </c>
       <c r="F59">
-        <v>413.136</v>
+        <v>420.384</v>
       </c>
       <c r="G59">
         <v>27.2</v>
@@ -6125,37 +6125,37 @@
         <v>11.95</v>
       </c>
       <c r="M59">
-        <v>97.41746880000001</v>
+        <v>99.1265472</v>
       </c>
       <c r="N59">
-        <v>-85.46746880000001</v>
+        <v>-87.1765472</v>
       </c>
       <c r="O59">
-        <v>-17.09349376</v>
+        <v>-17.43530944</v>
       </c>
       <c r="P59">
-        <v>-68.37397504</v>
+        <v>-69.74123776</v>
       </c>
       <c r="Q59">
-        <v>-1.573975040000008</v>
+        <v>-2.941237760000007</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1496922875467862</v>
+        <v>0.1521659134407573</v>
       </c>
       <c r="T59">
-        <v>1.970798304187175</v>
+        <v>2.017722073334489</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02453358755303649</v>
+        <v>0.02411059466419103</v>
       </c>
       <c r="W59">
-        <v>0.230014980054994</v>
+        <v>0.2301147217781838</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1226679377651825</v>
+        <v>0.1205529733209552</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1973762222764646</v>
+        <v>0.1992762222764646</v>
       </c>
       <c r="C60">
-        <v>-167.0795727207519</v>
+        <v>-176.9561319916598</v>
       </c>
       <c r="D60">
-        <v>226.1044272792481</v>
+        <v>223.4758680083402</v>
       </c>
       <c r="E60">
-        <v>151.184</v>
+        <v>158.432</v>
       </c>
       <c r="F60">
-        <v>420.384</v>
+        <v>427.6319999999999</v>
       </c>
       <c r="G60">
         <v>27.2</v>
@@ -6207,37 +6207,37 @@
         <v>11.95</v>
       </c>
       <c r="M60">
-        <v>99.12654719999999</v>
+        <v>100.8356256</v>
       </c>
       <c r="N60">
-        <v>-87.17654719999999</v>
+        <v>-88.88562559999998</v>
       </c>
       <c r="O60">
-        <v>-17.43530944</v>
+        <v>-17.77712512</v>
       </c>
       <c r="P60">
-        <v>-69.74123775999999</v>
+        <v>-71.10850047999999</v>
       </c>
       <c r="Q60">
-        <v>-2.941237759999993</v>
+        <v>-4.308500479999992</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1521659134407573</v>
+        <v>0.1547602040124831</v>
       </c>
       <c r="T60">
-        <v>2.017722073334489</v>
+        <v>2.066934806830452</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02411059466419103</v>
+        <v>0.02370194051734034</v>
       </c>
       <c r="W60">
-        <v>0.2301147217781838</v>
+        <v>0.2302110824260112</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1205529733209552</v>
+        <v>0.1185097025867017</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1992762222764646</v>
+        <v>0.2011762222764646</v>
       </c>
       <c r="C61">
-        <v>-176.9561319916598</v>
+        <v>-186.7722773804698</v>
       </c>
       <c r="D61">
-        <v>223.4758680083402</v>
+        <v>220.9077226195301</v>
       </c>
       <c r="E61">
-        <v>158.432</v>
+        <v>165.6799999999999</v>
       </c>
       <c r="F61">
-        <v>427.6319999999999</v>
+        <v>434.8799999999999</v>
       </c>
       <c r="G61">
         <v>27.2</v>
@@ -6289,37 +6289,37 @@
         <v>11.95</v>
       </c>
       <c r="M61">
-        <v>100.8356256</v>
+        <v>102.544704</v>
       </c>
       <c r="N61">
-        <v>-88.88562559999998</v>
+        <v>-90.59470399999999</v>
       </c>
       <c r="O61">
-        <v>-17.77712512</v>
+        <v>-18.1189408</v>
       </c>
       <c r="P61">
-        <v>-71.10850047999999</v>
+        <v>-72.47576319999999</v>
       </c>
       <c r="Q61">
-        <v>-4.308500479999992</v>
+        <v>-5.675763199999992</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1547602040124831</v>
+        <v>0.1574842091127951</v>
       </c>
       <c r="T61">
-        <v>2.066934806830452</v>
+        <v>2.118608177001213</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02370194051734034</v>
+        <v>0.02330690817538467</v>
       </c>
       <c r="W61">
-        <v>0.2302110824260112</v>
+        <v>0.2303042310522443</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1185097025867017</v>
+        <v>0.1165345408769233</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2011762222764646</v>
+        <v>0.2030762222764647</v>
       </c>
       <c r="C62">
-        <v>-186.7722773804698</v>
+        <v>-196.5300680211143</v>
       </c>
       <c r="D62">
-        <v>220.9077226195301</v>
+        <v>218.3979319788857</v>
       </c>
       <c r="E62">
-        <v>165.6799999999999</v>
+        <v>172.928</v>
       </c>
       <c r="F62">
-        <v>434.8799999999999</v>
+        <v>442.128</v>
       </c>
       <c r="G62">
         <v>27.2</v>
@@ -6371,37 +6371,37 @@
         <v>11.95</v>
       </c>
       <c r="M62">
-        <v>102.544704</v>
+        <v>104.2537824</v>
       </c>
       <c r="N62">
-        <v>-90.59470399999999</v>
+        <v>-92.3037824</v>
       </c>
       <c r="O62">
-        <v>-18.1189408</v>
+        <v>-18.46075648</v>
       </c>
       <c r="P62">
-        <v>-72.47576319999999</v>
+        <v>-73.84302592</v>
       </c>
       <c r="Q62">
-        <v>-5.675763199999992</v>
+        <v>-7.043025920000005</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1574842091127951</v>
+        <v>0.160347906782354</v>
       </c>
       <c r="T62">
-        <v>2.118608177001213</v>
+        <v>2.172931463590988</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02330690817538467</v>
+        <v>0.02292482771349311</v>
       </c>
       <c r="W62">
-        <v>0.2303042310522443</v>
+        <v>0.2303943256251583</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1165345408769233</v>
+        <v>0.1146241385674656</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2030762222764647</v>
+        <v>0.2049762222764646</v>
       </c>
       <c r="C63">
-        <v>-196.5300680211143</v>
+        <v>-206.2314705212953</v>
       </c>
       <c r="D63">
-        <v>218.3979319788857</v>
+        <v>215.9445294787047</v>
       </c>
       <c r="E63">
-        <v>172.928</v>
+        <v>180.176</v>
       </c>
       <c r="F63">
-        <v>442.128</v>
+        <v>449.376</v>
       </c>
       <c r="G63">
         <v>27.2</v>
@@ -6453,37 +6453,37 @@
         <v>11.95</v>
       </c>
       <c r="M63">
-        <v>104.2537824</v>
+        <v>105.9628608</v>
       </c>
       <c r="N63">
-        <v>-92.3037824</v>
+        <v>-94.0128608</v>
       </c>
       <c r="O63">
-        <v>-18.46075648</v>
+        <v>-18.80257216</v>
       </c>
       <c r="P63">
-        <v>-73.84302592</v>
+        <v>-75.21028864</v>
       </c>
       <c r="Q63">
-        <v>-7.043025920000005</v>
+        <v>-8.410288640000005</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.160347906782354</v>
+        <v>0.1633623253818896</v>
       </c>
       <c r="T63">
-        <v>2.172931463590988</v>
+        <v>2.230113870527593</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02292482771349311</v>
+        <v>0.02255507242779161</v>
       </c>
       <c r="W63">
-        <v>0.2303943256251583</v>
+        <v>0.2304815139215267</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1146241385674656</v>
+        <v>0.112775362138958</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2049762222764646</v>
+        <v>0.2068762222764646</v>
       </c>
       <c r="C64">
-        <v>-206.2314705212953</v>
+        <v>-215.8783641017804</v>
       </c>
       <c r="D64">
-        <v>215.9445294787047</v>
+        <v>213.5456358982195</v>
       </c>
       <c r="E64">
-        <v>180.176</v>
+        <v>187.424</v>
       </c>
       <c r="F64">
-        <v>449.376</v>
+        <v>456.624</v>
       </c>
       <c r="G64">
         <v>27.2</v>
@@ -6535,37 +6535,37 @@
         <v>11.95</v>
       </c>
       <c r="M64">
-        <v>105.9628608</v>
+        <v>107.6719392</v>
       </c>
       <c r="N64">
-        <v>-94.0128608</v>
+        <v>-95.72193919999999</v>
       </c>
       <c r="O64">
-        <v>-18.80257216</v>
+        <v>-19.14438784</v>
       </c>
       <c r="P64">
-        <v>-75.21028864</v>
+        <v>-76.57755136</v>
       </c>
       <c r="Q64">
-        <v>-8.410288640000005</v>
+        <v>-9.777551360000004</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1633623253818896</v>
+        <v>0.1665396855273461</v>
       </c>
       <c r="T64">
-        <v>2.230113870527593</v>
+        <v>2.29038721837969</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02255507242779161</v>
+        <v>0.02219705540512825</v>
       </c>
       <c r="W64">
-        <v>0.2304815139215267</v>
+        <v>0.2305659343354708</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.112775362138958</v>
+        <v>0.1109852770256413</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2068762222764646</v>
+        <v>0.2087762222764646</v>
       </c>
       <c r="C65">
-        <v>-215.8783641017804</v>
+        <v>-225.472545396914</v>
       </c>
       <c r="D65">
-        <v>213.5456358982195</v>
+        <v>211.199454603086</v>
       </c>
       <c r="E65">
-        <v>187.424</v>
+        <v>194.672</v>
       </c>
       <c r="F65">
-        <v>456.624</v>
+        <v>463.872</v>
       </c>
       <c r="G65">
         <v>27.2</v>
@@ -6617,37 +6617,37 @@
         <v>11.95</v>
       </c>
       <c r="M65">
-        <v>107.6719392</v>
+        <v>109.3810176</v>
       </c>
       <c r="N65">
-        <v>-95.72193919999999</v>
+        <v>-97.43101759999999</v>
       </c>
       <c r="O65">
-        <v>-19.14438784</v>
+        <v>-19.48620352</v>
       </c>
       <c r="P65">
-        <v>-76.57755136</v>
+        <v>-77.94481407999999</v>
       </c>
       <c r="Q65">
-        <v>-9.777551360000004</v>
+        <v>-11.14481407999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1665396855273461</v>
+        <v>0.1698935656808835</v>
       </c>
       <c r="T65">
-        <v>2.29038721837969</v>
+        <v>2.354009085556904</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02219705540512825</v>
+        <v>0.02185022641442312</v>
       </c>
       <c r="W65">
-        <v>0.2305659343354708</v>
+        <v>0.230647716611479</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1109852770256413</v>
+        <v>0.1092511320721157</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2087762222764646</v>
+        <v>0.2106762222764647</v>
       </c>
       <c r="C66">
-        <v>-225.472545396914</v>
+        <v>-235.0157329421113</v>
       </c>
       <c r="D66">
-        <v>211.199454603086</v>
+        <v>208.9042670578887</v>
       </c>
       <c r="E66">
-        <v>194.672</v>
+        <v>201.92</v>
       </c>
       <c r="F66">
-        <v>463.872</v>
+        <v>471.12</v>
       </c>
       <c r="G66">
         <v>27.2</v>
@@ -6699,37 +6699,37 @@
         <v>11.95</v>
       </c>
       <c r="M66">
-        <v>109.3810176</v>
+        <v>111.090096</v>
       </c>
       <c r="N66">
-        <v>-97.43101759999999</v>
+        <v>-99.140096</v>
       </c>
       <c r="O66">
-        <v>-19.48620352</v>
+        <v>-19.8280192</v>
       </c>
       <c r="P66">
-        <v>-77.94481407999999</v>
+        <v>-79.3120768</v>
       </c>
       <c r="Q66">
-        <v>-11.14481407999999</v>
+        <v>-12.5120768</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1698935656808835</v>
+        <v>0.1734390961289088</v>
       </c>
       <c r="T66">
-        <v>2.354009085556904</v>
+        <v>2.421266488001387</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02185022641442312</v>
+        <v>0.02151406908497046</v>
       </c>
       <c r="W66">
-        <v>0.230647716611479</v>
+        <v>0.230726982509764</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1092511320721157</v>
+        <v>0.1075703454248523</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2106762222764647</v>
+        <v>0.2125762222764647</v>
       </c>
       <c r="C67">
-        <v>-235.0157329421113</v>
+        <v>-244.5095713718961</v>
       </c>
       <c r="D67">
-        <v>208.9042670578887</v>
+        <v>206.6584286281039</v>
       </c>
       <c r="E67">
-        <v>201.92</v>
+        <v>209.168</v>
       </c>
       <c r="F67">
-        <v>471.12</v>
+        <v>478.368</v>
       </c>
       <c r="G67">
         <v>27.2</v>
@@ -6781,37 +6781,37 @@
         <v>11.95</v>
       </c>
       <c r="M67">
-        <v>111.090096</v>
+        <v>112.7991744</v>
       </c>
       <c r="N67">
-        <v>-99.140096</v>
+        <v>-100.8491744</v>
       </c>
       <c r="O67">
-        <v>-19.8280192</v>
+        <v>-20.16983488</v>
       </c>
       <c r="P67">
-        <v>-79.3120768</v>
+        <v>-80.67933952</v>
       </c>
       <c r="Q67">
-        <v>-12.5120768</v>
+        <v>-13.87933952</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1734390961289088</v>
+        <v>0.1771931871915237</v>
       </c>
       <c r="T67">
-        <v>2.421266488001387</v>
+        <v>2.492480208236722</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02151406908497046</v>
+        <v>0.02118809834125879</v>
       </c>
       <c r="W67">
-        <v>0.230726982509764</v>
+        <v>0.2308038464111312</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1075703454248523</v>
+        <v>0.1059404917062939</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2125762222764647</v>
+        <v>0.2144762222764646</v>
       </c>
       <c r="C68">
-        <v>-244.5095713718961</v>
+        <v>-253.9556353500315</v>
       </c>
       <c r="D68">
-        <v>206.6584286281039</v>
+        <v>204.4603646499685</v>
       </c>
       <c r="E68">
-        <v>209.168</v>
+        <v>216.416</v>
       </c>
       <c r="F68">
-        <v>478.368</v>
+        <v>485.616</v>
       </c>
       <c r="G68">
         <v>27.2</v>
@@ -6863,37 +6863,37 @@
         <v>11.95</v>
       </c>
       <c r="M68">
-        <v>112.7991744</v>
+        <v>114.5082528</v>
       </c>
       <c r="N68">
-        <v>-100.8491744</v>
+        <v>-102.5582528</v>
       </c>
       <c r="O68">
-        <v>-20.16983488</v>
+        <v>-20.51165056</v>
       </c>
       <c r="P68">
-        <v>-80.67933952</v>
+        <v>-82.04660224</v>
       </c>
       <c r="Q68">
-        <v>-13.87933952</v>
+        <v>-15.24660224</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1771931871915237</v>
+        <v>0.1811747989246002</v>
       </c>
       <c r="T68">
-        <v>2.492480208236722</v>
+        <v>2.568009911516622</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02118809834125879</v>
+        <v>0.02087185806750865</v>
       </c>
       <c r="W68">
-        <v>0.2308038464111312</v>
+        <v>0.2308784158676815</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1059404917062939</v>
+        <v>0.1043592903375433</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2144762222764646</v>
+        <v>0.2163762222764647</v>
       </c>
       <c r="C69">
-        <v>-253.9556353500315</v>
+        <v>-263.3554332514778</v>
       </c>
       <c r="D69">
-        <v>204.4603646499685</v>
+        <v>202.3085667485222</v>
       </c>
       <c r="E69">
-        <v>216.416</v>
+        <v>223.664</v>
       </c>
       <c r="F69">
-        <v>485.616</v>
+        <v>492.864</v>
       </c>
       <c r="G69">
         <v>27.2</v>
@@ -6945,37 +6945,37 @@
         <v>11.95</v>
       </c>
       <c r="M69">
-        <v>114.5082528</v>
+        <v>116.2173312</v>
       </c>
       <c r="N69">
-        <v>-102.5582528</v>
+        <v>-104.2673312</v>
       </c>
       <c r="O69">
-        <v>-20.51165056</v>
+        <v>-20.85346624</v>
       </c>
       <c r="P69">
-        <v>-82.04660224</v>
+        <v>-83.41386496000001</v>
       </c>
       <c r="Q69">
-        <v>-15.24660224</v>
+        <v>-16.61386496000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1811747989246002</v>
+        <v>0.1854052613909939</v>
       </c>
       <c r="T69">
-        <v>2.568009911516622</v>
+        <v>2.648260221251517</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02087185806750865</v>
+        <v>0.02056491897828058</v>
       </c>
       <c r="W69">
-        <v>0.2308784158676815</v>
+        <v>0.2309507921049214</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1043592903375433</v>
+        <v>0.1028245948914029</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2163762222764647</v>
+        <v>0.2182762222764646</v>
       </c>
       <c r="C70">
-        <v>-263.3554332514778</v>
+        <v>-272.7104106142735</v>
       </c>
       <c r="D70">
-        <v>202.3085667485222</v>
+        <v>200.2015893857265</v>
       </c>
       <c r="E70">
-        <v>223.664</v>
+        <v>230.912</v>
       </c>
       <c r="F70">
-        <v>492.864</v>
+        <v>500.112</v>
       </c>
       <c r="G70">
         <v>27.2</v>
@@ -7027,37 +7027,37 @@
         <v>11.95</v>
       </c>
       <c r="M70">
-        <v>116.2173312</v>
+        <v>117.9264096</v>
       </c>
       <c r="N70">
-        <v>-104.2673312</v>
+        <v>-105.9764096</v>
       </c>
       <c r="O70">
-        <v>-20.85346624</v>
+        <v>-21.19528192</v>
       </c>
       <c r="P70">
-        <v>-83.41386496000001</v>
+        <v>-84.78112768000001</v>
       </c>
       <c r="Q70">
-        <v>-16.61386496000002</v>
+        <v>-17.98112768000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1854052613909939</v>
+        <v>0.1899086569197357</v>
       </c>
       <c r="T70">
-        <v>2.648260221251517</v>
+        <v>2.733687970324147</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02056491897828058</v>
+        <v>0.02026687667424754</v>
       </c>
       <c r="W70">
-        <v>0.2309507921049214</v>
+        <v>0.2310210704802124</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1028245948914029</v>
+        <v>0.1013343833712377</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2182762222764646</v>
+        <v>0.2201762222764647</v>
       </c>
       <c r="C71">
-        <v>-272.7104106142735</v>
+        <v>-282.021953377938</v>
       </c>
       <c r="D71">
-        <v>200.2015893857265</v>
+        <v>198.1380466220621</v>
       </c>
       <c r="E71">
-        <v>230.912</v>
+        <v>238.16</v>
       </c>
       <c r="F71">
-        <v>500.112</v>
+        <v>507.36</v>
       </c>
       <c r="G71">
         <v>27.2</v>
@@ -7109,37 +7109,37 @@
         <v>11.95</v>
       </c>
       <c r="M71">
-        <v>117.9264096</v>
+        <v>119.635488</v>
       </c>
       <c r="N71">
-        <v>-105.9764096</v>
+        <v>-107.685488</v>
       </c>
       <c r="O71">
-        <v>-21.19528192</v>
+        <v>-21.5370976</v>
       </c>
       <c r="P71">
-        <v>-84.78112768000001</v>
+        <v>-86.14839040000001</v>
       </c>
       <c r="Q71">
-        <v>-17.98112768000001</v>
+        <v>-19.34839040000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1899086569197357</v>
+        <v>0.1947122788170602</v>
       </c>
       <c r="T71">
-        <v>2.733687970324147</v>
+        <v>2.824810902668285</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02026687667424754</v>
+        <v>0.01997734986461543</v>
       </c>
       <c r="W71">
-        <v>0.2310210704802124</v>
+        <v>0.2310893409019237</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1013343833712377</v>
+        <v>0.09988674932307717</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2201762222764647</v>
+        <v>0.2220762222764647</v>
       </c>
       <c r="C72">
-        <v>-282.021953377938</v>
+        <v>-291.2913909236419</v>
       </c>
       <c r="D72">
-        <v>198.1380466220621</v>
+        <v>196.1166090763581</v>
       </c>
       <c r="E72">
-        <v>238.16</v>
+        <v>245.4080000000001</v>
       </c>
       <c r="F72">
-        <v>507.36</v>
+        <v>514.6080000000001</v>
       </c>
       <c r="G72">
         <v>27.2</v>
@@ -7191,37 +7191,37 @@
         <v>11.95</v>
       </c>
       <c r="M72">
-        <v>119.635488</v>
+        <v>121.3445664</v>
       </c>
       <c r="N72">
-        <v>-107.685488</v>
+        <v>-109.3945664</v>
       </c>
       <c r="O72">
-        <v>-21.5370976</v>
+        <v>-21.87891328000001</v>
       </c>
       <c r="P72">
-        <v>-86.14839040000001</v>
+        <v>-87.51565312000001</v>
       </c>
       <c r="Q72">
-        <v>-19.34839040000001</v>
+        <v>-20.71565312000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1947122788170602</v>
+        <v>0.1998471849831658</v>
       </c>
       <c r="T72">
-        <v>2.824810902668285</v>
+        <v>2.922218175174088</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01997734986461543</v>
+        <v>0.01969597873976169</v>
       </c>
       <c r="W72">
-        <v>0.2310893409019237</v>
+        <v>0.2311556882131642</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.09988674932307717</v>
+        <v>0.09847989369880839</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2220762222764646</v>
+        <v>0.2239762222764647</v>
       </c>
       <c r="C73">
-        <v>-291.2913909236418</v>
+        <v>-300.5199989301594</v>
       </c>
       <c r="D73">
-        <v>196.1166090763582</v>
+        <v>194.1360010698406</v>
       </c>
       <c r="E73">
-        <v>245.408</v>
+        <v>252.656</v>
       </c>
       <c r="F73">
-        <v>514.6079999999999</v>
+        <v>521.856</v>
       </c>
       <c r="G73">
         <v>27.2</v>
@@ -7273,37 +7273,37 @@
         <v>11.95</v>
       </c>
       <c r="M73">
-        <v>121.3445664</v>
+        <v>123.0536448</v>
       </c>
       <c r="N73">
-        <v>-109.3945664</v>
+        <v>-111.1036448</v>
       </c>
       <c r="O73">
-        <v>-21.87891328</v>
+        <v>-22.22072896</v>
       </c>
       <c r="P73">
-        <v>-87.51565312</v>
+        <v>-88.88291584</v>
       </c>
       <c r="Q73">
-        <v>-20.71565312</v>
+        <v>-22.08291584</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1998471849831657</v>
+        <v>0.2053488701611359</v>
       </c>
       <c r="T73">
-        <v>2.922218175174087</v>
+        <v>3.026583110001733</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01969597873976169</v>
+        <v>0.01942242347948722</v>
       </c>
       <c r="W73">
-        <v>0.2311556882131642</v>
+        <v>0.2312201925435369</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.0984798936988085</v>
+        <v>0.09711211739743608</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2239762222764647</v>
+        <v>0.2258762222764646</v>
       </c>
       <c r="C74">
-        <v>-300.5199989301594</v>
+        <v>-309.7090020584939</v>
       </c>
       <c r="D74">
-        <v>194.1360010698406</v>
+        <v>192.1949979415061</v>
       </c>
       <c r="E74">
-        <v>252.656</v>
+        <v>259.9039999999999</v>
       </c>
       <c r="F74">
-        <v>521.856</v>
+        <v>529.1039999999999</v>
       </c>
       <c r="G74">
         <v>27.2</v>
@@ -7355,37 +7355,37 @@
         <v>11.95</v>
       </c>
       <c r="M74">
-        <v>123.0536448</v>
+        <v>124.7627232</v>
       </c>
       <c r="N74">
-        <v>-111.1036448</v>
+        <v>-112.8127232</v>
       </c>
       <c r="O74">
-        <v>-22.22072896</v>
+        <v>-22.56254464</v>
       </c>
       <c r="P74">
-        <v>-88.88291584</v>
+        <v>-90.25017855999998</v>
       </c>
       <c r="Q74">
-        <v>-22.08291584</v>
+        <v>-23.45017855999998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2053488701611359</v>
+        <v>0.2112580875745113</v>
       </c>
       <c r="T74">
-        <v>3.026583110001733</v>
+        <v>3.138678780742538</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01942242347948722</v>
+        <v>0.01915636288387781</v>
       </c>
       <c r="W74">
-        <v>0.2312201925435369</v>
+        <v>0.2312829296319816</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.09711211739743608</v>
+        <v>0.09578181441938904</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2258762222764646</v>
+        <v>0.2277762222764646</v>
       </c>
       <c r="C75">
-        <v>-309.7090020584939</v>
+        <v>-318.8595764770507</v>
       </c>
       <c r="D75">
-        <v>192.1949979415061</v>
+        <v>190.2924235229493</v>
       </c>
       <c r="E75">
-        <v>259.9039999999999</v>
+        <v>267.152</v>
       </c>
       <c r="F75">
-        <v>529.1039999999999</v>
+        <v>536.352</v>
       </c>
       <c r="G75">
         <v>27.2</v>
@@ -7437,37 +7437,37 @@
         <v>11.95</v>
       </c>
       <c r="M75">
-        <v>124.7627232</v>
+        <v>126.4718016</v>
       </c>
       <c r="N75">
-        <v>-112.8127232</v>
+        <v>-114.5218016</v>
       </c>
       <c r="O75">
-        <v>-22.56254464</v>
+        <v>-22.90436032</v>
       </c>
       <c r="P75">
-        <v>-90.25017855999998</v>
+        <v>-91.61744128000001</v>
       </c>
       <c r="Q75">
-        <v>-23.45017855999998</v>
+        <v>-24.81744128000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2112580875745113</v>
+        <v>0.217621860173531</v>
       </c>
       <c r="T75">
-        <v>3.138678780742538</v>
+        <v>3.259397195386482</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01915636288387781</v>
+        <v>0.01889749311517676</v>
       </c>
       <c r="W75">
-        <v>0.2312829296319816</v>
+        <v>0.2313439711234413</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.09578181441938904</v>
+        <v>0.09448746557588372</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2277762222764646</v>
+        <v>0.2296762222764647</v>
       </c>
       <c r="C76">
-        <v>-318.8595764770507</v>
+        <v>-327.9728522382968</v>
       </c>
       <c r="D76">
-        <v>190.2924235229493</v>
+        <v>188.4271477617031</v>
       </c>
       <c r="E76">
-        <v>267.152</v>
+        <v>274.3999999999999</v>
       </c>
       <c r="F76">
-        <v>536.352</v>
+        <v>543.5999999999999</v>
       </c>
       <c r="G76">
         <v>27.2</v>
@@ -7519,37 +7519,37 @@
         <v>11.95</v>
       </c>
       <c r="M76">
-        <v>126.4718016</v>
+        <v>128.18088</v>
       </c>
       <c r="N76">
-        <v>-114.5218016</v>
+        <v>-116.23088</v>
       </c>
       <c r="O76">
-        <v>-22.90436032</v>
+        <v>-23.24617599999999</v>
       </c>
       <c r="P76">
-        <v>-91.61744128000001</v>
+        <v>-92.98470399999998</v>
       </c>
       <c r="Q76">
-        <v>-24.81744128000001</v>
+        <v>-26.18470399999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.217621860173531</v>
+        <v>0.2244947345804723</v>
       </c>
       <c r="T76">
-        <v>3.259397195386482</v>
+        <v>3.389773083201941</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01889749311517676</v>
+        <v>0.01864552654030774</v>
       </c>
       <c r="W76">
-        <v>0.2313439711234413</v>
+        <v>0.2314033848417955</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.09448746557588372</v>
+        <v>0.09322763270153867</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2296762222764647</v>
+        <v>0.2315762222764647</v>
       </c>
       <c r="C77">
-        <v>-327.9728522382968</v>
+        <v>-337.0499155169992</v>
       </c>
       <c r="D77">
-        <v>188.4271477617031</v>
+        <v>186.5980844830008</v>
       </c>
       <c r="E77">
-        <v>274.3999999999999</v>
+        <v>281.648</v>
       </c>
       <c r="F77">
-        <v>543.5999999999999</v>
+        <v>550.848</v>
       </c>
       <c r="G77">
         <v>27.2</v>
@@ -7601,37 +7601,37 @@
         <v>11.95</v>
       </c>
       <c r="M77">
-        <v>128.18088</v>
+        <v>129.8899584</v>
       </c>
       <c r="N77">
-        <v>-116.23088</v>
+        <v>-117.9399584</v>
       </c>
       <c r="O77">
-        <v>-23.24617599999999</v>
+        <v>-23.58799168</v>
       </c>
       <c r="P77">
-        <v>-92.98470399999998</v>
+        <v>-94.35196671999998</v>
       </c>
       <c r="Q77">
-        <v>-26.18470399999998</v>
+        <v>-27.55196671999998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2244947345804723</v>
+        <v>0.2319403485213253</v>
       </c>
       <c r="T77">
-        <v>3.389773083201941</v>
+        <v>3.531013628335355</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01864552654030774</v>
+        <v>0.01840019066477737</v>
       </c>
       <c r="W77">
-        <v>0.2314033848417955</v>
+        <v>0.2314612350412455</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.09322763270153867</v>
+        <v>0.0920009533238868</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2315762222764647</v>
+        <v>0.2334762222764646</v>
       </c>
       <c r="C78">
-        <v>-337.0499155169992</v>
+        <v>-346.0918107193565</v>
       </c>
       <c r="D78">
-        <v>186.5980844830008</v>
+        <v>184.8041892806435</v>
       </c>
       <c r="E78">
-        <v>281.648</v>
+        <v>288.896</v>
       </c>
       <c r="F78">
-        <v>550.848</v>
+        <v>558.096</v>
       </c>
       <c r="G78">
         <v>27.2</v>
@@ -7683,37 +7683,37 @@
         <v>11.95</v>
       </c>
       <c r="M78">
-        <v>129.8899584</v>
+        <v>131.5990368</v>
       </c>
       <c r="N78">
-        <v>-117.9399584</v>
+        <v>-119.6490368</v>
       </c>
       <c r="O78">
-        <v>-23.58799168</v>
+        <v>-23.92980736</v>
       </c>
       <c r="P78">
-        <v>-94.35196671999998</v>
+        <v>-95.71922943999999</v>
       </c>
       <c r="Q78">
-        <v>-27.55196671999998</v>
+        <v>-28.91922944</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2319403485213253</v>
+        <v>0.2400334071526873</v>
       </c>
       <c r="T78">
-        <v>3.531013628335355</v>
+        <v>3.68453596000211</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01840019066477737</v>
+        <v>0.01816122714965039</v>
       </c>
       <c r="W78">
-        <v>0.2314612350412455</v>
+        <v>0.2315175826381125</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.0920009533238868</v>
+        <v>0.09080613574825191</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2334762222764646</v>
+        <v>0.2353762222764647</v>
       </c>
       <c r="C79">
-        <v>-346.0918107193565</v>
+        <v>-355.0995424716305</v>
       </c>
       <c r="D79">
-        <v>184.8041892806435</v>
+        <v>183.0444575283695</v>
       </c>
       <c r="E79">
-        <v>288.896</v>
+        <v>296.1439999999999</v>
       </c>
       <c r="F79">
-        <v>558.096</v>
+        <v>565.3439999999999</v>
       </c>
       <c r="G79">
         <v>27.2</v>
@@ -7765,37 +7765,37 @@
         <v>11.95</v>
       </c>
       <c r="M79">
-        <v>131.5990368</v>
+        <v>133.3081152</v>
       </c>
       <c r="N79">
-        <v>-119.6490368</v>
+        <v>-121.3581152</v>
       </c>
       <c r="O79">
-        <v>-23.92980736</v>
+        <v>-24.27162304</v>
       </c>
       <c r="P79">
-        <v>-95.71922943999999</v>
+        <v>-97.08649216000001</v>
       </c>
       <c r="Q79">
-        <v>-28.91922944</v>
+        <v>-30.28649216000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2400334071526873</v>
+        <v>0.2488621983869003</v>
       </c>
       <c r="T79">
-        <v>3.68453596000211</v>
+        <v>3.852014867274933</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01816122714965039</v>
+        <v>0.01792839090414205</v>
       </c>
       <c r="W79">
-        <v>0.2315175826381125</v>
+        <v>0.2315724854248033</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.09080613574825191</v>
+        <v>0.08964195452071022</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2353762222764647</v>
+        <v>0.2372762222764646</v>
       </c>
       <c r="C80">
-        <v>-355.0995424716305</v>
+        <v>-364.0740774962325</v>
       </c>
       <c r="D80">
-        <v>183.0444575283695</v>
+        <v>181.3179225037675</v>
       </c>
       <c r="E80">
-        <v>296.1439999999999</v>
+        <v>303.392</v>
       </c>
       <c r="F80">
-        <v>565.3439999999999</v>
+        <v>572.592</v>
       </c>
       <c r="G80">
         <v>27.2</v>
@@ -7847,37 +7847,37 @@
         <v>11.95</v>
       </c>
       <c r="M80">
-        <v>133.3081152</v>
+        <v>135.0171936</v>
       </c>
       <c r="N80">
-        <v>-121.3581152</v>
+        <v>-123.0671936</v>
       </c>
       <c r="O80">
-        <v>-24.27162304</v>
+        <v>-24.61343872</v>
       </c>
       <c r="P80">
-        <v>-97.08649216000001</v>
+        <v>-98.45375488000001</v>
       </c>
       <c r="Q80">
-        <v>-30.28649216000001</v>
+        <v>-31.65375488000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2488621983869003</v>
+        <v>0.2585318268815145</v>
       </c>
       <c r="T80">
-        <v>3.852014867274933</v>
+        <v>4.035444146668977</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01792839090414205</v>
+        <v>0.01770144924712759</v>
       </c>
       <c r="W80">
-        <v>0.2315724854248033</v>
+        <v>0.2316259982675273</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.08964195452071022</v>
+        <v>0.08850724623563799</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2372762222764646</v>
+        <v>0.2391762222764647</v>
       </c>
       <c r="C81">
-        <v>-364.0740774962325</v>
+        <v>-373.0163463826277</v>
       </c>
       <c r="D81">
-        <v>181.3179225037675</v>
+        <v>179.6236536173723</v>
       </c>
       <c r="E81">
-        <v>303.392</v>
+        <v>310.64</v>
       </c>
       <c r="F81">
-        <v>572.592</v>
+        <v>579.84</v>
       </c>
       <c r="G81">
         <v>27.2</v>
@@ -7929,37 +7929,37 @@
         <v>11.95</v>
       </c>
       <c r="M81">
-        <v>135.0171936</v>
+        <v>136.726272</v>
       </c>
       <c r="N81">
-        <v>-123.0671936</v>
+        <v>-124.776272</v>
       </c>
       <c r="O81">
-        <v>-24.61343872</v>
+        <v>-24.9552544</v>
       </c>
       <c r="P81">
-        <v>-98.45375488000001</v>
+        <v>-99.82101760000002</v>
       </c>
       <c r="Q81">
-        <v>-31.65375488000001</v>
+        <v>-33.02101760000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2585318268815145</v>
+        <v>0.2691684182255903</v>
       </c>
       <c r="T81">
-        <v>4.035444146668977</v>
+        <v>4.237216354002427</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01770144924712759</v>
+        <v>0.0174801811315385</v>
       </c>
       <c r="W81">
-        <v>0.2316259982675273</v>
+        <v>0.2316781732891832</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.08850724623563799</v>
+        <v>0.08740090565769243</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2391762222764647</v>
+        <v>0.2410762222764647</v>
       </c>
       <c r="C82">
-        <v>-373.0163463826277</v>
+        <v>-381.9272452598708</v>
       </c>
       <c r="D82">
-        <v>179.6236536173723</v>
+        <v>177.9607547401291</v>
       </c>
       <c r="E82">
-        <v>310.64</v>
+        <v>317.888</v>
       </c>
       <c r="F82">
-        <v>579.84</v>
+        <v>587.088</v>
       </c>
       <c r="G82">
         <v>27.2</v>
@@ -8011,37 +8011,37 @@
         <v>11.95</v>
       </c>
       <c r="M82">
-        <v>136.726272</v>
+        <v>138.4353504</v>
       </c>
       <c r="N82">
-        <v>-124.776272</v>
+        <v>-126.4853504</v>
       </c>
       <c r="O82">
-        <v>-24.9552544</v>
+        <v>-25.29707008</v>
       </c>
       <c r="P82">
-        <v>-99.82101760000002</v>
+        <v>-101.18828032</v>
       </c>
       <c r="Q82">
-        <v>-33.02101760000002</v>
+        <v>-34.38828032000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2691684182255903</v>
+        <v>0.2809246507637793</v>
       </c>
       <c r="T82">
-        <v>4.237216354002427</v>
+        <v>4.460227741055187</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0174801811315385</v>
+        <v>0.01726437642621086</v>
       </c>
       <c r="W82">
-        <v>0.2316781732891832</v>
+        <v>0.2317290600386995</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.08740090565769243</v>
+        <v>0.08632188213105429</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2410762222764647</v>
+        <v>0.2429762222764647</v>
       </c>
       <c r="C83">
-        <v>-381.9272452598708</v>
+        <v>-390.8076373770938</v>
       </c>
       <c r="D83">
-        <v>177.9607547401291</v>
+        <v>176.3283626229062</v>
       </c>
       <c r="E83">
-        <v>317.888</v>
+        <v>325.136</v>
       </c>
       <c r="F83">
-        <v>587.088</v>
+        <v>594.336</v>
       </c>
       <c r="G83">
         <v>27.2</v>
@@ -8093,37 +8093,37 @@
         <v>11.95</v>
       </c>
       <c r="M83">
-        <v>138.4353504</v>
+        <v>140.1444288</v>
       </c>
       <c r="N83">
-        <v>-126.4853504</v>
+        <v>-128.1944288</v>
       </c>
       <c r="O83">
-        <v>-25.29707008</v>
+        <v>-25.63888576000001</v>
       </c>
       <c r="P83">
-        <v>-101.18828032</v>
+        <v>-102.55554304</v>
       </c>
       <c r="Q83">
-        <v>-34.38828032000001</v>
+        <v>-35.75554304000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2809246507637793</v>
+        <v>0.2939871313617671</v>
       </c>
       <c r="T83">
-        <v>4.460227741055187</v>
+        <v>4.708018171113808</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01726437642621086</v>
+        <v>0.01705383525028146</v>
       </c>
       <c r="W83">
-        <v>0.2317290600386995</v>
+        <v>0.2317787056479836</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.08632188213105429</v>
+        <v>0.08526917625140717</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2429762222764647</v>
+        <v>0.2448762222764647</v>
       </c>
       <c r="C84">
-        <v>-390.8076373770938</v>
+        <v>-399.6583545977965</v>
       </c>
       <c r="D84">
-        <v>176.3283626229062</v>
+        <v>174.7256454022036</v>
       </c>
       <c r="E84">
-        <v>325.136</v>
+        <v>332.3840000000001</v>
       </c>
       <c r="F84">
-        <v>594.336</v>
+        <v>601.5840000000001</v>
       </c>
       <c r="G84">
         <v>27.2</v>
@@ -8175,37 +8175,37 @@
         <v>11.95</v>
       </c>
       <c r="M84">
-        <v>140.1444288</v>
+        <v>141.8535072</v>
       </c>
       <c r="N84">
-        <v>-128.1944288</v>
+        <v>-129.9035072</v>
       </c>
       <c r="O84">
-        <v>-25.63888576000001</v>
+        <v>-25.98070144000001</v>
       </c>
       <c r="P84">
-        <v>-102.55554304</v>
+        <v>-103.92280576</v>
       </c>
       <c r="Q84">
-        <v>-35.75554304000002</v>
+        <v>-37.12280576000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2939871313617671</v>
+        <v>0.3085863743830475</v>
       </c>
       <c r="T84">
-        <v>4.708018171113808</v>
+        <v>4.984960416473444</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01705383525028146</v>
+        <v>0.01684836735569976</v>
       </c>
       <c r="W84">
-        <v>0.2317787056479836</v>
+        <v>0.231827154977526</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.08526917625140717</v>
+        <v>0.08424183677849872</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2448762222764647</v>
+        <v>0.2467762222764646</v>
       </c>
       <c r="C85">
-        <v>-399.6583545977965</v>
+        <v>-408.4801988133804</v>
       </c>
       <c r="D85">
-        <v>174.7256454022036</v>
+        <v>173.1518011866196</v>
       </c>
       <c r="E85">
-        <v>332.3840000000001</v>
+        <v>339.632</v>
       </c>
       <c r="F85">
-        <v>601.5840000000001</v>
+        <v>608.832</v>
       </c>
       <c r="G85">
         <v>27.2</v>
@@ -8257,37 +8257,37 @@
         <v>11.95</v>
       </c>
       <c r="M85">
-        <v>141.8535072</v>
+        <v>143.5625856</v>
       </c>
       <c r="N85">
-        <v>-129.9035072</v>
+        <v>-131.6125856</v>
       </c>
       <c r="O85">
-        <v>-25.98070144000001</v>
+        <v>-26.32251712</v>
       </c>
       <c r="P85">
-        <v>-103.92280576</v>
+        <v>-105.29006848</v>
       </c>
       <c r="Q85">
-        <v>-37.12280576000003</v>
+        <v>-38.49006847999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3085863743830475</v>
+        <v>0.3250105227819881</v>
       </c>
       <c r="T85">
-        <v>4.984960416473444</v>
+        <v>5.296520442503036</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01684836735569976</v>
+        <v>0.01664779155384619</v>
       </c>
       <c r="W85">
-        <v>0.231827154977526</v>
+        <v>0.2318744507516031</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.08424183677849872</v>
+        <v>0.08323895776923107</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2467762222764646</v>
+        <v>0.2486762222764646</v>
       </c>
       <c r="C86">
-        <v>-408.4801988133804</v>
+        <v>-417.2739432809697</v>
       </c>
       <c r="D86">
-        <v>173.1518011866196</v>
+        <v>171.6060567190303</v>
       </c>
       <c r="E86">
-        <v>339.632</v>
+        <v>346.8799999999999</v>
       </c>
       <c r="F86">
-        <v>608.832</v>
+        <v>616.0799999999999</v>
       </c>
       <c r="G86">
         <v>27.2</v>
@@ -8339,37 +8339,37 @@
         <v>11.95</v>
       </c>
       <c r="M86">
-        <v>143.5625856</v>
+        <v>145.271664</v>
       </c>
       <c r="N86">
-        <v>-131.6125856</v>
+        <v>-133.321664</v>
       </c>
       <c r="O86">
-        <v>-26.32251712</v>
+        <v>-26.6643328</v>
       </c>
       <c r="P86">
-        <v>-105.29006848</v>
+        <v>-106.6573312</v>
       </c>
       <c r="Q86">
-        <v>-38.49006847999999</v>
+        <v>-39.8573312</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3250105227819879</v>
+        <v>0.3436245576341204</v>
       </c>
       <c r="T86">
-        <v>5.296520442503033</v>
+        <v>5.649621805336568</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01664779155384619</v>
+        <v>0.01645193518262447</v>
       </c>
       <c r="W86">
-        <v>0.2318744507516031</v>
+        <v>0.2319206336839372</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.08323895776923107</v>
+        <v>0.08225967591312222</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2486762222764646</v>
+        <v>0.2505762222764646</v>
       </c>
       <c r="C87">
-        <v>-417.2739432809697</v>
+        <v>-426.0403338902076</v>
       </c>
       <c r="D87">
-        <v>171.6060567190303</v>
+        <v>170.0876661097923</v>
       </c>
       <c r="E87">
-        <v>346.8799999999999</v>
+        <v>354.128</v>
       </c>
       <c r="F87">
-        <v>616.0799999999999</v>
+        <v>623.328</v>
       </c>
       <c r="G87">
         <v>27.2</v>
@@ -8421,37 +8421,37 @@
         <v>11.95</v>
       </c>
       <c r="M87">
-        <v>145.271664</v>
+        <v>146.9807424</v>
       </c>
       <c r="N87">
-        <v>-133.321664</v>
+        <v>-135.0307424</v>
       </c>
       <c r="O87">
-        <v>-26.6643328</v>
+        <v>-27.00614848</v>
       </c>
       <c r="P87">
-        <v>-106.6573312</v>
+        <v>-108.02459392</v>
       </c>
       <c r="Q87">
-        <v>-39.8573312</v>
+        <v>-41.22459392</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3436245576341204</v>
+        <v>0.3648977403222718</v>
       </c>
       <c r="T87">
-        <v>5.649621805336568</v>
+        <v>6.053166220003466</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01645193518262447</v>
+        <v>0.01626063361073349</v>
       </c>
       <c r="W87">
-        <v>0.2319206336839372</v>
+        <v>0.231965742594589</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.08225967591312222</v>
+        <v>0.08130316805366733</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2505762222764646</v>
+        <v>0.2524762222764647</v>
       </c>
       <c r="C88">
-        <v>-426.0403338902076</v>
+        <v>-434.7800903633914</v>
       </c>
       <c r="D88">
-        <v>170.0876661097923</v>
+        <v>168.5959096366086</v>
       </c>
       <c r="E88">
-        <v>354.128</v>
+        <v>361.3759999999999</v>
       </c>
       <c r="F88">
-        <v>623.328</v>
+        <v>630.5759999999999</v>
       </c>
       <c r="G88">
         <v>27.2</v>
@@ -8503,37 +8503,37 @@
         <v>11.95</v>
       </c>
       <c r="M88">
-        <v>146.9807424</v>
+        <v>148.6898208</v>
       </c>
       <c r="N88">
-        <v>-135.0307424</v>
+        <v>-136.7398208</v>
       </c>
       <c r="O88">
-        <v>-27.00614848</v>
+        <v>-27.34796415999999</v>
       </c>
       <c r="P88">
-        <v>-108.02459392</v>
+        <v>-109.39185664</v>
       </c>
       <c r="Q88">
-        <v>-41.22459392</v>
+        <v>-42.59185663999997</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3648977403222718</v>
+        <v>0.389443720347062</v>
       </c>
       <c r="T88">
-        <v>6.053166220003466</v>
+        <v>6.518794390772963</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01626063361073349</v>
+        <v>0.01607372977612736</v>
       </c>
       <c r="W88">
-        <v>0.231965742594589</v>
+        <v>0.2320098145187892</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.08130316805366733</v>
+        <v>0.08036864888063688</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2524762222764647</v>
+        <v>0.2543762222764646</v>
       </c>
       <c r="C89">
-        <v>-434.7800903633914</v>
+        <v>-443.493907393001</v>
       </c>
       <c r="D89">
-        <v>168.5959096366086</v>
+        <v>167.130092606999</v>
       </c>
       <c r="E89">
-        <v>361.3759999999999</v>
+        <v>368.624</v>
       </c>
       <c r="F89">
-        <v>630.5759999999999</v>
+        <v>637.824</v>
       </c>
       <c r="G89">
         <v>27.2</v>
@@ -8585,37 +8585,37 @@
         <v>11.95</v>
       </c>
       <c r="M89">
-        <v>148.6898208</v>
+        <v>150.3988992</v>
       </c>
       <c r="N89">
-        <v>-136.7398208</v>
+        <v>-138.4488992</v>
       </c>
       <c r="O89">
-        <v>-27.34796415999999</v>
+        <v>-27.68977984</v>
       </c>
       <c r="P89">
-        <v>-109.39185664</v>
+        <v>-110.75911936</v>
       </c>
       <c r="Q89">
-        <v>-42.59185663999997</v>
+        <v>-43.95911935999997</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.389443720347062</v>
+        <v>0.4180806970426506</v>
       </c>
       <c r="T89">
-        <v>6.518794390772963</v>
+        <v>7.062027256670711</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01607372977612736</v>
+        <v>0.01589107375594409</v>
       </c>
       <c r="W89">
-        <v>0.2320098145187892</v>
+        <v>0.2320528848083484</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.08036864888063688</v>
+        <v>0.07945536877972059</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2543762222764646</v>
+        <v>0.2562762222764646</v>
       </c>
       <c r="C90">
-        <v>-443.493907393001</v>
+        <v>-452.1824557203998</v>
       </c>
       <c r="D90">
-        <v>167.130092606999</v>
+        <v>165.6895442796001</v>
       </c>
       <c r="E90">
-        <v>368.624</v>
+        <v>375.872</v>
       </c>
       <c r="F90">
-        <v>637.824</v>
+        <v>645.072</v>
       </c>
       <c r="G90">
         <v>27.2</v>
@@ -8667,37 +8667,37 @@
         <v>11.95</v>
       </c>
       <c r="M90">
-        <v>150.3988992</v>
+        <v>152.1079776</v>
       </c>
       <c r="N90">
-        <v>-138.4488992</v>
+        <v>-140.1579776</v>
       </c>
       <c r="O90">
-        <v>-27.68977984</v>
+        <v>-28.03159552</v>
       </c>
       <c r="P90">
-        <v>-110.75911936</v>
+        <v>-112.12638208</v>
       </c>
       <c r="Q90">
-        <v>-43.95911935999997</v>
+        <v>-45.32638207999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4180806970426506</v>
+        <v>0.4519243967738006</v>
       </c>
       <c r="T90">
-        <v>7.062027256670711</v>
+        <v>7.704029734549867</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01589107375594409</v>
+        <v>0.01571252236542786</v>
       </c>
       <c r="W90">
-        <v>0.2320528848083484</v>
+        <v>0.2320949872262321</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.07945536877972059</v>
+        <v>0.07856261182713942</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2562762222764646</v>
+        <v>0.2581762222764646</v>
       </c>
       <c r="C91">
-        <v>-452.1824557203998</v>
+        <v>-460.8463831592255</v>
       </c>
       <c r="D91">
-        <v>165.6895442796001</v>
+        <v>164.2736168407745</v>
       </c>
       <c r="E91">
-        <v>375.872</v>
+        <v>383.1199999999999</v>
       </c>
       <c r="F91">
-        <v>645.072</v>
+        <v>652.3199999999999</v>
       </c>
       <c r="G91">
         <v>27.2</v>
@@ -8749,37 +8749,37 @@
         <v>11.95</v>
       </c>
       <c r="M91">
-        <v>152.1079776</v>
+        <v>153.817056</v>
       </c>
       <c r="N91">
-        <v>-140.1579776</v>
+        <v>-141.867056</v>
       </c>
       <c r="O91">
-        <v>-28.03159552</v>
+        <v>-28.3734112</v>
       </c>
       <c r="P91">
-        <v>-112.12638208</v>
+        <v>-113.4936448</v>
       </c>
       <c r="Q91">
-        <v>-45.32638207999999</v>
+        <v>-46.6936448</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4519243967738006</v>
+        <v>0.4925368364511806</v>
       </c>
       <c r="T91">
-        <v>7.704029734549867</v>
+        <v>8.474432708004853</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01571252236542786</v>
+        <v>0.01553793878358978</v>
       </c>
       <c r="W91">
-        <v>0.2320949872262321</v>
+        <v>0.2321361540348295</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.07856261182713942</v>
+        <v>0.07768969391794878</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2581762222764646</v>
+        <v>0.2600762222764647</v>
       </c>
       <c r="C92">
-        <v>-460.8463831592255</v>
+        <v>-469.4863155667528</v>
       </c>
       <c r="D92">
-        <v>164.2736168407745</v>
+        <v>162.8816844332473</v>
       </c>
       <c r="E92">
-        <v>383.1199999999999</v>
+        <v>390.368</v>
       </c>
       <c r="F92">
-        <v>652.3199999999999</v>
+        <v>659.568</v>
       </c>
       <c r="G92">
         <v>27.2</v>
@@ -8831,37 +8831,37 @@
         <v>11.95</v>
       </c>
       <c r="M92">
-        <v>153.817056</v>
+        <v>155.5261344</v>
       </c>
       <c r="N92">
-        <v>-141.867056</v>
+        <v>-143.5761344</v>
       </c>
       <c r="O92">
-        <v>-28.3734112</v>
+        <v>-28.71522688</v>
       </c>
       <c r="P92">
-        <v>-113.4936448</v>
+        <v>-114.86090752</v>
       </c>
       <c r="Q92">
-        <v>-46.6936448</v>
+        <v>-48.06090752</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4925368364511806</v>
+        <v>0.5421742627235342</v>
       </c>
       <c r="T92">
-        <v>8.474432708004853</v>
+        <v>9.416036342227617</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01553793878358978</v>
+        <v>0.01536719220355033</v>
       </c>
       <c r="W92">
-        <v>0.2321361540348295</v>
+        <v>0.2321764160784028</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.07768969391794878</v>
+        <v>0.07683596101775159</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2600762222764647</v>
+        <v>0.2619762222764647</v>
       </c>
       <c r="C93">
-        <v>-469.4863155667528</v>
+        <v>-478.1028577662866</v>
       </c>
       <c r="D93">
-        <v>162.8816844332473</v>
+        <v>161.5131422337134</v>
       </c>
       <c r="E93">
-        <v>390.368</v>
+        <v>397.616</v>
       </c>
       <c r="F93">
-        <v>659.568</v>
+        <v>666.816</v>
       </c>
       <c r="G93">
         <v>27.2</v>
@@ -8913,37 +8913,37 @@
         <v>11.95</v>
       </c>
       <c r="M93">
-        <v>155.5261344</v>
+        <v>157.2352128</v>
       </c>
       <c r="N93">
-        <v>-143.5761344</v>
+        <v>-145.2852128</v>
       </c>
       <c r="O93">
-        <v>-28.71522688</v>
+        <v>-29.05704256</v>
       </c>
       <c r="P93">
-        <v>-114.86090752</v>
+        <v>-116.22817024</v>
       </c>
       <c r="Q93">
-        <v>-48.06090752</v>
+        <v>-49.42817024000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5421742627235342</v>
+        <v>0.604221045563976</v>
       </c>
       <c r="T93">
-        <v>9.416036342227617</v>
+        <v>10.59304088500607</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01536719220355033</v>
+        <v>0.01520015750568565</v>
       </c>
       <c r="W93">
-        <v>0.2321764160784028</v>
+        <v>0.2322158028601594</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.07683596101775159</v>
+        <v>0.07600078752842832</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2619762222764647</v>
+        <v>0.2638762222764646</v>
       </c>
       <c r="C94">
-        <v>-478.1028577662866</v>
+        <v>-486.696594423444</v>
       </c>
       <c r="D94">
-        <v>161.5131422337134</v>
+        <v>160.167405576556</v>
       </c>
       <c r="E94">
-        <v>397.616</v>
+        <v>404.864</v>
       </c>
       <c r="F94">
-        <v>666.816</v>
+        <v>674.064</v>
       </c>
       <c r="G94">
         <v>27.2</v>
@@ -8995,37 +8995,37 @@
         <v>11.95</v>
       </c>
       <c r="M94">
-        <v>157.2352128</v>
+        <v>158.9442912</v>
       </c>
       <c r="N94">
-        <v>-145.2852128</v>
+        <v>-146.9942912</v>
       </c>
       <c r="O94">
-        <v>-29.05704256</v>
+        <v>-29.39885824000001</v>
       </c>
       <c r="P94">
-        <v>-116.22817024</v>
+        <v>-117.59543296</v>
       </c>
       <c r="Q94">
-        <v>-49.42817024000001</v>
+        <v>-50.79543296000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.604221045563976</v>
+        <v>0.6839954806445442</v>
       </c>
       <c r="T94">
-        <v>10.59304088500607</v>
+        <v>12.10633244000694</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01520015750568565</v>
+        <v>0.01503671495186108</v>
       </c>
       <c r="W94">
-        <v>0.2322158028601594</v>
+        <v>0.2322543426143512</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.07600078752842832</v>
+        <v>0.07518357475930526</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2638762222764646</v>
+        <v>0.2657762222764646</v>
       </c>
       <c r="C95">
-        <v>-486.696594423444</v>
+        <v>-495.2680908789894</v>
       </c>
       <c r="D95">
-        <v>160.167405576556</v>
+        <v>158.8439091210106</v>
       </c>
       <c r="E95">
-        <v>404.864</v>
+        <v>412.112</v>
       </c>
       <c r="F95">
-        <v>674.064</v>
+        <v>681.312</v>
       </c>
       <c r="G95">
         <v>27.2</v>
@@ -9077,37 +9077,37 @@
         <v>11.95</v>
       </c>
       <c r="M95">
-        <v>158.9442912</v>
+        <v>160.6533696</v>
       </c>
       <c r="N95">
-        <v>-146.9942912</v>
+        <v>-148.7033696</v>
       </c>
       <c r="O95">
-        <v>-29.39885824000001</v>
+        <v>-29.74067392000001</v>
       </c>
       <c r="P95">
-        <v>-117.59543296</v>
+        <v>-118.96269568</v>
       </c>
       <c r="Q95">
-        <v>-50.79543296000001</v>
+        <v>-52.16269568000003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6839954806445442</v>
+        <v>0.7903613940853015</v>
       </c>
       <c r="T95">
-        <v>12.10633244000694</v>
+        <v>14.12405451334143</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01503671495186108</v>
+        <v>0.0148767498991817</v>
       </c>
       <c r="W95">
-        <v>0.2322543426143512</v>
+        <v>0.232292062373773</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.07518357475930526</v>
+        <v>0.07438374949590842</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2657762222764646</v>
+        <v>0.2676762222764646</v>
       </c>
       <c r="C96">
-        <v>-495.2680908789894</v>
+        <v>-503.8178939407177</v>
       </c>
       <c r="D96">
-        <v>158.8439091210106</v>
+        <v>157.5421060592824</v>
       </c>
       <c r="E96">
-        <v>412.112</v>
+        <v>419.3600000000001</v>
       </c>
       <c r="F96">
-        <v>681.312</v>
+        <v>688.5600000000001</v>
       </c>
       <c r="G96">
         <v>27.2</v>
@@ -9159,37 +9159,37 @@
         <v>11.95</v>
       </c>
       <c r="M96">
-        <v>160.6533696</v>
+        <v>162.362448</v>
       </c>
       <c r="N96">
-        <v>-148.7033696</v>
+        <v>-150.412448</v>
       </c>
       <c r="O96">
-        <v>-29.74067392000001</v>
+        <v>-30.08248960000001</v>
       </c>
       <c r="P96">
-        <v>-118.96269568</v>
+        <v>-120.3299584</v>
       </c>
       <c r="Q96">
-        <v>-52.16269568000003</v>
+        <v>-53.52995840000004</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7903613940853015</v>
+        <v>0.9392736729023623</v>
       </c>
       <c r="T96">
-        <v>14.12405451334143</v>
+        <v>16.94886541600973</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0148767498991817</v>
+        <v>0.01472015253182189</v>
       </c>
       <c r="W96">
-        <v>0.232292062373773</v>
+        <v>0.2323289880329964</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.07438374949590842</v>
+        <v>0.07360076265910942</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2676762222764646</v>
+        <v>0.2695762222764647</v>
       </c>
       <c r="C97">
-        <v>-503.8178939407177</v>
+        <v>-512.3465326367138</v>
       </c>
       <c r="D97">
-        <v>157.5421060592824</v>
+        <v>156.2614673632862</v>
       </c>
       <c r="E97">
-        <v>419.3600000000001</v>
+        <v>426.608</v>
       </c>
       <c r="F97">
-        <v>688.5600000000001</v>
+        <v>695.808</v>
       </c>
       <c r="G97">
         <v>27.2</v>
@@ -9241,37 +9241,37 @@
         <v>11.95</v>
       </c>
       <c r="M97">
-        <v>162.362448</v>
+        <v>164.0715264</v>
       </c>
       <c r="N97">
-        <v>-150.412448</v>
+        <v>-152.1215264</v>
       </c>
       <c r="O97">
-        <v>-30.08248960000001</v>
+        <v>-30.42430528</v>
       </c>
       <c r="P97">
-        <v>-120.3299584</v>
+        <v>-121.69722112</v>
       </c>
       <c r="Q97">
-        <v>-53.52995840000004</v>
+        <v>-54.89722112</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9392736729023623</v>
+        <v>1.162642091127954</v>
       </c>
       <c r="T97">
-        <v>16.94886541600973</v>
+        <v>21.18608177001217</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01472015253182189</v>
+        <v>0.01456681760961542</v>
       </c>
       <c r="W97">
-        <v>0.2323289880329964</v>
+        <v>0.2323651444076527</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.07360076265910942</v>
+        <v>0.07283408804807712</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2695762222764646</v>
+        <v>0.2714762222764646</v>
       </c>
       <c r="C98">
-        <v>-512.3465326367136</v>
+        <v>-520.854518932171</v>
       </c>
       <c r="D98">
-        <v>156.2614673632863</v>
+        <v>155.0014810678289</v>
       </c>
       <c r="E98">
-        <v>426.6079999999999</v>
+        <v>433.8559999999999</v>
       </c>
       <c r="F98">
-        <v>695.8079999999999</v>
+        <v>703.0559999999999</v>
       </c>
       <c r="G98">
         <v>27.2</v>
@@ -9323,37 +9323,37 @@
         <v>11.95</v>
       </c>
       <c r="M98">
-        <v>164.0715264</v>
+        <v>165.7806048</v>
       </c>
       <c r="N98">
-        <v>-152.1215264</v>
+        <v>-153.8306048</v>
       </c>
       <c r="O98">
-        <v>-30.42430528</v>
+        <v>-30.76612096</v>
       </c>
       <c r="P98">
-        <v>-121.69722112</v>
+        <v>-123.06448384</v>
       </c>
       <c r="Q98">
-        <v>-54.89722112</v>
+        <v>-56.26448384000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.16264209112795</v>
+        <v>1.534922788170601</v>
       </c>
       <c r="T98">
-        <v>21.18608177001211</v>
+        <v>28.24810902668282</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01456681760961542</v>
+        <v>0.0144166442321967</v>
       </c>
       <c r="W98">
-        <v>0.2323651444076527</v>
+        <v>0.232400555290048</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.07283408804807701</v>
+        <v>0.07208322116098342</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2714762222764646</v>
+        <v>0.2733762222764646</v>
       </c>
       <c r="C99">
-        <v>-520.854518932171</v>
+        <v>-529.342348411806</v>
       </c>
       <c r="D99">
-        <v>155.0014810678289</v>
+        <v>153.761651588194</v>
       </c>
       <c r="E99">
-        <v>433.8559999999999</v>
+        <v>441.104</v>
       </c>
       <c r="F99">
-        <v>703.0559999999999</v>
+        <v>710.304</v>
       </c>
       <c r="G99">
         <v>27.2</v>
@@ -9405,37 +9405,37 @@
         <v>11.95</v>
       </c>
       <c r="M99">
-        <v>165.7806048</v>
+        <v>167.4896832</v>
       </c>
       <c r="N99">
-        <v>-153.8306048</v>
+        <v>-155.5396832</v>
       </c>
       <c r="O99">
-        <v>-30.76612096</v>
+        <v>-31.10793664000001</v>
       </c>
       <c r="P99">
-        <v>-123.06448384</v>
+        <v>-124.43174656</v>
       </c>
       <c r="Q99">
-        <v>-56.26448384000001</v>
+        <v>-57.63174656000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.534922788170601</v>
+        <v>2.279484182255901</v>
       </c>
       <c r="T99">
-        <v>28.24810902668282</v>
+        <v>42.37216354002422</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0144166442321967</v>
+        <v>0.01426953561758245</v>
       </c>
       <c r="W99">
-        <v>0.232400555290048</v>
+        <v>0.2324352435013741</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.07208322116098342</v>
+        <v>0.0713476780879122</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2733762222764646</v>
+        <v>0.2752762222764646</v>
       </c>
       <c r="C100">
-        <v>-529.342348411806</v>
+        <v>-537.8105009297822</v>
       </c>
       <c r="D100">
-        <v>153.761651588194</v>
+        <v>152.5414990702178</v>
       </c>
       <c r="E100">
-        <v>441.104</v>
+        <v>448.3519999999999</v>
       </c>
       <c r="F100">
-        <v>710.304</v>
+        <v>717.5519999999999</v>
       </c>
       <c r="G100">
         <v>27.2</v>
@@ -9487,37 +9487,37 @@
         <v>11.95</v>
       </c>
       <c r="M100">
-        <v>167.4896832</v>
+        <v>169.1987616</v>
       </c>
       <c r="N100">
-        <v>-155.5396832</v>
+        <v>-157.2487616</v>
       </c>
       <c r="O100">
-        <v>-31.10793664000001</v>
+        <v>-31.44975231999999</v>
       </c>
       <c r="P100">
-        <v>-124.43174656</v>
+        <v>-125.79900928</v>
       </c>
       <c r="Q100">
-        <v>-57.63174656000001</v>
+        <v>-58.99900927999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.279484182255901</v>
+        <v>4.513168364511801</v>
       </c>
       <c r="T100">
-        <v>42.37216354002422</v>
+        <v>84.74432708004845</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01426953561758245</v>
+        <v>0.01412539889417253</v>
       </c>
       <c r="W100">
-        <v>0.2324352435013741</v>
+        <v>0.2324692309407541</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.0713476780879122</v>
+        <v>0.07062699447086274</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2752762222764646</v>
-      </c>
-      <c r="C101">
-        <v>-537.8105009297822</v>
-      </c>
-      <c r="D101">
-        <v>152.5414990702178</v>
-      </c>
-      <c r="E101">
-        <v>448.3519999999999</v>
-      </c>
-      <c r="F101">
-        <v>717.5519999999999</v>
-      </c>
-      <c r="G101">
-        <v>27.2</v>
-      </c>
-      <c r="H101">
-        <v>455.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>78.75</v>
-      </c>
-      <c r="K101">
-        <v>66.8</v>
-      </c>
-      <c r="L101">
-        <v>11.95</v>
-      </c>
-      <c r="M101">
-        <v>169.1987616</v>
-      </c>
-      <c r="N101">
-        <v>-157.2487616</v>
-      </c>
-      <c r="O101">
-        <v>-31.44975231999999</v>
-      </c>
-      <c r="P101">
-        <v>-125.79900928</v>
-      </c>
-      <c r="Q101">
-        <v>-58.99900927999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.513168364511801</v>
-      </c>
-      <c r="T101">
-        <v>84.74432708004845</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01412539889417253</v>
-      </c>
-      <c r="W101">
-        <v>0.2324692309407541</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07062699447086274</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
